--- a/Assets/Data/Commodore 128/250477/Data C128DCR 250477.xlsx
+++ b/Assets/Data/Commodore 128/250477/Data C128DCR 250477.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore 128\250477\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore 128\250477\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38349401-D7A8-4EDB-8CE2-1019364B5DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A44B702-E70E-4020-997A-661F58767C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5941" uniqueCount="1888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6055" uniqueCount="1916">
   <si>
     <t>Name</t>
   </si>
@@ -5153,6 +5153,710 @@
     <t>Commodore shared files/Component images/74LS03-secondary.jpg</t>
   </si>
   <si>
+    <t>243482e2-bf29-412d-9b70-f1d1720fdffe</t>
+  </si>
+  <si>
+    <t>99a5c159-573d-4983-beab-e33036f8b027</t>
+  </si>
+  <si>
+    <t>68Ω 1/4W 5%</t>
+  </si>
+  <si>
+    <t>390Ω 1/4W 5%</t>
+  </si>
+  <si>
+    <t>110Ω 1W 5%</t>
+  </si>
+  <si>
+    <t>47KΩ 5%</t>
+  </si>
+  <si>
+    <t>560Ω 5%</t>
+  </si>
+  <si>
+    <t>10KΩ 5%</t>
+  </si>
+  <si>
+    <t>1KΩ 5%</t>
+  </si>
+  <si>
+    <t>100Ω 5%</t>
+  </si>
+  <si>
+    <t>120Ω 5%</t>
+  </si>
+  <si>
+    <t>47Ω 5%</t>
+  </si>
+  <si>
+    <t>82Ω 5%</t>
+  </si>
+  <si>
+    <t>330Ω 5%</t>
+  </si>
+  <si>
+    <t>470KΩ 5%</t>
+  </si>
+  <si>
+    <t>100KΩ 5%</t>
+  </si>
+  <si>
+    <t>68Ω 5%</t>
+  </si>
+  <si>
+    <t>180Ω 5%</t>
+  </si>
+  <si>
+    <t>4.7KΩ 5%</t>
+  </si>
+  <si>
+    <t>1MΩ 5%</t>
+  </si>
+  <si>
+    <t>620Ω 5%</t>
+  </si>
+  <si>
+    <t>33KΩ 5%</t>
+  </si>
+  <si>
+    <t>360Ω 5%</t>
+  </si>
+  <si>
+    <t>39KΩ 5%</t>
+  </si>
+  <si>
+    <t>2.4KΩ 5%</t>
+  </si>
+  <si>
+    <t>3.9KΩ 5%</t>
+  </si>
+  <si>
+    <t>240Ω 5%</t>
+  </si>
+  <si>
+    <t>390Ω 5%</t>
+  </si>
+  <si>
+    <t>390Ω 1/2W 5%</t>
+  </si>
+  <si>
+    <t>3.3KΩ 5%</t>
+  </si>
+  <si>
+    <t>150Ω 5%</t>
+  </si>
+  <si>
+    <t>43KΩ 5%</t>
+  </si>
+  <si>
+    <t>470Ω 1/2W 5%</t>
+  </si>
+  <si>
+    <t>1KΩ</t>
+  </si>
+  <si>
+    <t>3.3KΩ</t>
+  </si>
+  <si>
+    <t>33Ω</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_68_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_390_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_110_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_47k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_560_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_10k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_1k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_100_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_120_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_47_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_82_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_330_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_470k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_100k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_180_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_4k7_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_1m_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_620_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_33k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_360_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_39k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_2k4_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_3k9_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_240_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_3k3_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_150_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_43k_5.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_470_5.png</t>
+  </si>
+  <si>
+    <t>29798145-14d2-4ccf-b284-666c1feecf11</t>
+  </si>
+  <si>
+    <t>0d47aa33-7e62-4406-95f3-9cacbe319b63</t>
+  </si>
+  <si>
+    <t>b4d41d84-ba61-49c6-a25c-3f7b2584c0cd</t>
+  </si>
+  <si>
+    <t>07d90e04-8d04-46d6-84bb-c7856875035c</t>
+  </si>
+  <si>
+    <t>9d3a62a1-cf47-48c0-bb76-ab07671c68f6</t>
+  </si>
+  <si>
+    <t>ad069483-3f80-47d5-813e-f82eb7b2294a</t>
+  </si>
+  <si>
+    <t>aca0b262-c348-4a93-8348-ce8ed11c981f</t>
+  </si>
+  <si>
+    <t>6f727b6f-dbfe-4549-9d65-0530f96c235e</t>
+  </si>
+  <si>
+    <t>fb34d637-a5da-4935-9846-3428ecd88469</t>
+  </si>
+  <si>
+    <t>6e8b3746-3474-4095-be41-56c0f610a1dd</t>
+  </si>
+  <si>
+    <t>634ef6e0-213d-4dc4-8964-8b5399e0fb26</t>
+  </si>
+  <si>
+    <t>1b77f300-27fe-46c7-9abb-401d941fe6b8</t>
+  </si>
+  <si>
+    <t>36232bd5-2100-42d4-9a9e-35d60fc21b37</t>
+  </si>
+  <si>
+    <t>c1c076d1-103c-4798-b109-1b8fca366a68</t>
+  </si>
+  <si>
+    <t>d959f284-7792-4696-8275-0f5df4914aaf</t>
+  </si>
+  <si>
+    <t>6a204d07-0623-4325-ba4f-436f32dcb452</t>
+  </si>
+  <si>
+    <t>12a2dc02-6fce-49c3-bb25-b3d9164c3581</t>
+  </si>
+  <si>
+    <t>fc80809f-7dee-42d9-a4ff-063f7cf81ea0</t>
+  </si>
+  <si>
+    <t>cad31e64-95f8-4008-94d5-3b6718317571</t>
+  </si>
+  <si>
+    <t>16d061b2-345a-40f4-9289-0e408f916b34</t>
+  </si>
+  <si>
+    <t>d4af3d2b-b01c-4025-aadd-e74ac62e52eb</t>
+  </si>
+  <si>
+    <t>f1c3c6fd-dfc2-4ca5-a026-24890e54e53f</t>
+  </si>
+  <si>
+    <t>6e9d74e4-3102-43eb-9932-7dc4b0b7b354</t>
+  </si>
+  <si>
+    <t>e01d6f1c-3122-40d5-8ddc-4f8543b3f3da</t>
+  </si>
+  <si>
+    <t>898f4a0e-b6fa-4919-bdf7-249e181d0ba4</t>
+  </si>
+  <si>
+    <t>3a3974f2-db9d-4d79-852f-a009b546203d</t>
+  </si>
+  <si>
+    <t>0a6e89db-2c6f-47fd-8755-16ada556f3ab</t>
+  </si>
+  <si>
+    <t>21bb9399-ab72-4b6f-a523-938ce3b159d3</t>
+  </si>
+  <si>
+    <t>129f8830-73ae-4097-95c1-ce56b6011acd</t>
+  </si>
+  <si>
+    <t>914762b7-8082-4996-b5f9-12704f06e762</t>
+  </si>
+  <si>
+    <t>1d56065a-9d40-4f9f-a09f-d67887fb857c</t>
+  </si>
+  <si>
+    <t>e1aadd5c-1184-4795-9dcc-727b1ab25eb2</t>
+  </si>
+  <si>
+    <t>d6a02eb8-31be-41ec-97c3-828e926ff0dc</t>
+  </si>
+  <si>
+    <t>fa7bfa12-105e-45c7-95aa-5c93daff310e</t>
+  </si>
+  <si>
+    <t>66f0cc67-61b9-4c62-a059-947748234941</t>
+  </si>
+  <si>
+    <t>d740ea45-df70-4eaa-8e38-9a7f5f6c349c</t>
+  </si>
+  <si>
+    <t>4b7bcfe3-59a4-4b88-8247-8feeb1fdaed8</t>
+  </si>
+  <si>
+    <t>cc2747d2-a929-442a-8c12-9d3785d97cfe</t>
+  </si>
+  <si>
+    <t>fbf87602-7d64-4180-931d-d62ebb231d37</t>
+  </si>
+  <si>
+    <t>590a2fe4-3a5f-427a-83a4-0e904ebc49e6</t>
+  </si>
+  <si>
+    <t>b9ba8087-fbfd-4110-a8e5-f086f5560d1a</t>
+  </si>
+  <si>
+    <t>75c56f71-1cc1-4b72-b777-911209ae1ca1</t>
+  </si>
+  <si>
+    <t>6562e03d-c7fa-4419-93a2-35a7bb734738</t>
+  </si>
+  <si>
+    <t>61bc7a87-98aa-4ab2-ba25-22ca71843846</t>
+  </si>
+  <si>
+    <t>5f3b4ab3-8784-43be-8e0e-ef823b36d6b0</t>
+  </si>
+  <si>
+    <t>882d16a3-4205-4279-b4ca-3e47b0a2fa04</t>
+  </si>
+  <si>
+    <t>101dc684-f2d3-4d40-a61a-c69e652ecc88</t>
+  </si>
+  <si>
+    <t>6847c8e3-2f19-4ef2-b09b-5ef1a4357680</t>
+  </si>
+  <si>
+    <t>a6bce5c0-50ed-4687-a397-17ddcbf3e093</t>
+  </si>
+  <si>
+    <t>21a9b69b-1507-4423-a54c-8d5023bf3207</t>
+  </si>
+  <si>
+    <t>c6728aa0-9114-4595-a78c-4eb95a382be2</t>
+  </si>
+  <si>
+    <t>dad7ff17-db1e-4adb-87e6-bbb99bc7bf9d</t>
+  </si>
+  <si>
+    <t>9fd79cb1-9ff9-48d8-9c3c-0f69b8449934</t>
+  </si>
+  <si>
+    <t>431209f3-c032-4698-a389-07d385161743</t>
+  </si>
+  <si>
+    <t>e463cc33-1480-4ef3-9be0-44a4986af536</t>
+  </si>
+  <si>
+    <t>be43dfc1-6ccb-447c-9bcc-3f28fd8dbd47</t>
+  </si>
+  <si>
+    <t>e2e4fefe-9401-40cc-840f-21d0c1d6b6d8</t>
+  </si>
+  <si>
+    <t>20a44421-fc33-4095-8509-447cacb2463f</t>
+  </si>
+  <si>
+    <t>ab04ae07-8963-452b-86a3-b5b8e60eead8</t>
+  </si>
+  <si>
+    <t>001f86a5-576d-4230-ac12-e56baa7232c3</t>
+  </si>
+  <si>
+    <t>47880fe2-bfd1-4422-80d0-7db3f1f061a6</t>
+  </si>
+  <si>
+    <t>fc266b91-84b3-4cfd-97ac-1c9d3d5be099</t>
+  </si>
+  <si>
+    <t>3b3ef4ce-31b3-46da-a0cc-291d9cd652a2</t>
+  </si>
+  <si>
+    <t>16a6db1c-fa1a-4d9f-9f5a-5e4c4108b918</t>
+  </si>
+  <si>
+    <t>1a35d386-4fbb-4e5e-8f73-5c73e8f8ff82</t>
+  </si>
+  <si>
+    <t>37805f44-f37a-428f-8f64-459cfd180a73</t>
+  </si>
+  <si>
+    <t>bbf7fb07-aeef-453c-a8b1-e5275a6bcd2f</t>
+  </si>
+  <si>
+    <t>5f5ca01f-ab6b-4723-9565-b54982d34722</t>
+  </si>
+  <si>
+    <t>48c8fc6e-a4b6-4d8f-9069-6117f26c870e</t>
+  </si>
+  <si>
+    <t>8df5b7c3-bc1a-4d08-8edc-02c6f06ff6b5</t>
+  </si>
+  <si>
+    <t>38fc59d4-8373-4c12-850b-adb1c3b1ec31</t>
+  </si>
+  <si>
+    <t>c90508a3-ce9f-4e96-bb7d-bafc4fa25316</t>
+  </si>
+  <si>
+    <t>40eba650-a94f-45de-806b-eb1030f475b0</t>
+  </si>
+  <si>
+    <t>c3d10f14-494c-4703-8046-1c29ea4de096</t>
+  </si>
+  <si>
+    <t>ee888045-cf15-478d-8e9c-a912842c5abb</t>
+  </si>
+  <si>
+    <t>730887f9-6873-4662-8306-bc35dd361f34</t>
+  </si>
+  <si>
+    <t>98d22239-bf38-4aa0-8390-f36671c0eb5e</t>
+  </si>
+  <si>
+    <t>d0093a48-8fa5-4a7b-8c11-092508336fce</t>
+  </si>
+  <si>
+    <t>c086072d-ebff-4e15-85b5-5f7c5f0a6c96</t>
+  </si>
+  <si>
+    <t>4ea9e23f-c7a0-4edb-8c2a-6d8d4dd637a6</t>
+  </si>
+  <si>
+    <t>00a390b5-b6d9-4377-8db5-5b4820f2cbb7</t>
+  </si>
+  <si>
+    <t>353eacc6-a22a-4eaa-8691-a18a17f628b8</t>
+  </si>
+  <si>
+    <t>24fee2b5-4fcf-470d-87ff-8debf57b8502</t>
+  </si>
+  <si>
+    <t>ee13a804-429f-41f1-bd99-af3eb450d714</t>
+  </si>
+  <si>
+    <t>fdda808a-7654-453c-93e3-964a7741e5cd</t>
+  </si>
+  <si>
+    <t>362cd708-dc4a-4428-a5fa-2817bb57f28f</t>
+  </si>
+  <si>
+    <t>b9bdfabb-4089-4ba7-81b5-4e0d76533c90</t>
+  </si>
+  <si>
+    <t>b20be889-01f9-460b-a931-864926851e41</t>
+  </si>
+  <si>
+    <t>bedc7acb-cfe1-4e58-bd90-52675b4b5b0b</t>
+  </si>
+  <si>
+    <t>4c45621c-a9eb-46ba-850a-2d740cb51969</t>
+  </si>
+  <si>
+    <t>741bd2da-a1db-409c-9ed0-0d5a473afee5</t>
+  </si>
+  <si>
+    <t>12719651-68eb-46a8-9704-9617da7ce814</t>
+  </si>
+  <si>
+    <t>6743bca1-3196-4d73-9d96-bc3e4dd6c187</t>
+  </si>
+  <si>
+    <t>629c2189-d625-497d-a096-cd382eeacfe2</t>
+  </si>
+  <si>
+    <t>5a06b6af-4d94-4e73-828d-5f1b3b352fc5</t>
+  </si>
+  <si>
+    <t>e0f5df0e-614b-49f0-9e18-c7c21aa944d5</t>
+  </si>
+  <si>
+    <t>7f000740-76ab-4a0c-b9f0-671508ba1347</t>
+  </si>
+  <si>
+    <t>d37ac297-d703-46c3-939b-e7e74c6aac10</t>
+  </si>
+  <si>
+    <t>c270834e-2802-4233-b494-fcbee9f726a8</t>
+  </si>
+  <si>
+    <t>081e7c90-1172-4764-9c1f-29880facca4b</t>
+  </si>
+  <si>
+    <t>f230237a-8761-4ba3-8502-ad63b838daa4</t>
+  </si>
+  <si>
+    <t>aff248a0-f3b9-4fe5-b7b1-cf3ea9839df0</t>
+  </si>
+  <si>
+    <t>03d34980-4390-4591-9f7a-bebfd61eeff7</t>
+  </si>
+  <si>
+    <t>b1d0dd12-0947-4c9c-8710-a06ba59d7b92</t>
+  </si>
+  <si>
+    <t>e1d0e5b1-92c1-4116-baf9-6d69d7148e87</t>
+  </si>
+  <si>
+    <t>9e520ffd-1c05-48ff-90b5-9db26a1a3c71</t>
+  </si>
+  <si>
+    <t>41705140-fc1b-40fd-96f0-609ad2a3e182</t>
+  </si>
+  <si>
+    <t>b5616c20-2c94-4876-91a8-52a405215c79</t>
+  </si>
+  <si>
+    <t>cd095f21-0ec6-418a-bc4c-4837a3e44b41</t>
+  </si>
+  <si>
+    <t>ce67d7d3-80d7-4147-9cc2-2f2ab522ec74</t>
+  </si>
+  <si>
+    <t>d664472d-653f-406d-b36a-560e22349873</t>
+  </si>
+  <si>
+    <t>33767dd7-c96c-4d86-9b38-a7eb6f6035b2</t>
+  </si>
+  <si>
+    <t>b51c9bd1-3f71-42b5-bc06-977d8cc6c1da</t>
+  </si>
+  <si>
+    <t>fb10526b-e91c-44e8-a471-a9f298393b14</t>
+  </si>
+  <si>
+    <t>1275beac-ed3c-4064-b6b3-a34f8eaf0e51</t>
+  </si>
+  <si>
+    <t>696baa4e-0d8c-4347-be27-4562e3c015a9</t>
+  </si>
+  <si>
+    <t>4ce0f8ba-1794-41d2-a70c-95235c80ca4d</t>
+  </si>
+  <si>
+    <t>d1251977-0da4-4e1f-a6d6-101e743a4393</t>
+  </si>
+  <si>
+    <t>7e107c40-854b-4b4a-9d33-d829a077427f</t>
+  </si>
+  <si>
+    <t>b440d249-a9f8-407d-872b-589b749d49e4</t>
+  </si>
+  <si>
+    <t>7ef3a38f-83bf-40d3-8660-6c93c59e1645</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/C128 Keyboard matrix.png</t>
+  </si>
+  <si>
+    <t>Keyboard matrix</t>
+  </si>
+  <si>
+    <t>382eabc1-db16-4658-8b8d-ba2966fe0f95</t>
+  </si>
+  <si>
+    <t>Resistor pack, 8 pin</t>
+  </si>
+  <si>
+    <t>Resistor pack, 6 pin</t>
+  </si>
+  <si>
+    <t>Resistor pack, 9 pin</t>
+  </si>
+  <si>
+    <t>Resistor pack, 7 pin</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_pack_8pin.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_pack_7pin.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_pack_9pin.png</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/resistor_pack_6pin.png</t>
+  </si>
+  <si>
+    <t>9e2b8f16-82c7-4493-8cc8-4f1a71ca060a</t>
+  </si>
+  <si>
+    <t>b433bc07-19eb-402d-a7b6-786d716cb800</t>
+  </si>
+  <si>
+    <t>3b9f0451-1436-4784-b9d0-9a9b73fa6638</t>
+  </si>
+  <si>
+    <t>13a7828d-5627-4526-b418-fd21e9accc13</t>
+  </si>
+  <si>
+    <t>c3663a71-1852-4713-946e-5b0192088944</t>
+  </si>
+  <si>
+    <t>d81bb017-423c-46fe-afd1-6c36fda03e70</t>
+  </si>
+  <si>
+    <t>e595386d-a3ff-4d0a-9c7e-52b84ee60ff5</t>
+  </si>
+  <si>
+    <t>c096fc45-a4eb-4486-8e16-110ebcfb2bde</t>
+  </si>
+  <si>
+    <t>fc426b09-ae14-415c-a668-fd777dce0aef</t>
+  </si>
+  <si>
+    <t>Resistor packs must be mounted with GND pin at its designated position</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/8701-secondary.png</t>
+  </si>
+  <si>
+    <t>349608fd-68db-448c-8269-9133fb6695e4</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/Ferrite bead.png</t>
+  </si>
+  <si>
+    <t>0afbd139-22d5-4521-a169-61231b3bfcf8</t>
+  </si>
+  <si>
+    <t>7d68ca91-0804-4c46-98ef-fd20410ea61f</t>
+  </si>
+  <si>
+    <t>bb2b5555-d349-464b-a99b-de036b28b975</t>
+  </si>
+  <si>
+    <t>22e44224-b175-40f9-a867-a9983d9fd237</t>
+  </si>
+  <si>
+    <t>767747f9-c00e-423e-92ed-b5f2de3b8360</t>
+  </si>
+  <si>
+    <t>a97cba65-cac6-462d-8781-9c5787160c4c</t>
+  </si>
+  <si>
+    <t>da9a8cca-acee-49f4-84d6-69637d9dc169</t>
+  </si>
+  <si>
+    <t>fc80eada-a48f-4649-8306-d9a52846f2c2</t>
+  </si>
+  <si>
+    <t>3a858616-171d-47e7-928b-521d96f57728</t>
+  </si>
+  <si>
+    <t>f10e84d8-1b06-40e7-a85f-5b81eaac5a94</t>
+  </si>
+  <si>
+    <t>d0e7c6e2-caa5-4827-ad77-6777bef24793</t>
+  </si>
+  <si>
+    <t>43fae7c4-d36e-4003-8594-a5c132b72fda</t>
+  </si>
+  <si>
+    <t>ca657238-de42-4434-98e0-f7805c72e0fd</t>
+  </si>
+  <si>
+    <t>e9564c5a-9583-439b-be2d-200cc9f3ae2a</t>
+  </si>
+  <si>
+    <t>3814a794-6d12-4c5d-bf07-4d34c9994f62</t>
+  </si>
+  <si>
+    <t>e7f4c80c-84e6-4f6e-8b5e-109f43e104c3</t>
+  </si>
+  <si>
+    <t>6760cd0c-0e14-4840-a9b4-7685b430a760</t>
+  </si>
+  <si>
+    <t>41cd15b4-897d-403a-8c0a-7b36c5dc147a</t>
+  </si>
+  <si>
+    <t>e6ef473b-4501-4e83-bf61-081bb32c1005</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component images/EMI filter.png</t>
+  </si>
+  <si>
+    <t>a2d9b46b-a650-4f5f-bae7-2c88b798bf18</t>
+  </si>
+  <si>
+    <t>96af69d4-8464-4d93-a8d1-13e51a2745c0</t>
+  </si>
+  <si>
+    <t>7d043ad1-0e3e-41c4-8b72-76d9a338abfe</t>
+  </si>
+  <si>
+    <t>EMI filters have 3 terminals, where the middle one is ground. It does not matter how the two other terminals are mounted, and the component can be rotated. It has no polarity.
+Their purpose is to reduce high frequency noice.</t>
+  </si>
+  <si>
+    <t>Ferrite beads are non-polarized, so they have no + (plus) or – (minus) terminal and can be mounted in either direction. It has no polarity.
+Their purpose is to reduce high frequency noice.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -5165,626 +5869,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-April-25</t>
+      <t>2026-May-1</t>
     </r>
-  </si>
-  <si>
-    <t>243482e2-bf29-412d-9b70-f1d1720fdffe</t>
-  </si>
-  <si>
-    <t>99a5c159-573d-4983-beab-e33036f8b027</t>
-  </si>
-  <si>
-    <t>68Ω 1/4W 5%</t>
-  </si>
-  <si>
-    <t>390Ω 1/4W 5%</t>
-  </si>
-  <si>
-    <t>110Ω 1W 5%</t>
-  </si>
-  <si>
-    <t>47KΩ 5%</t>
-  </si>
-  <si>
-    <t>560Ω 5%</t>
-  </si>
-  <si>
-    <t>10KΩ 5%</t>
-  </si>
-  <si>
-    <t>1KΩ 5%</t>
-  </si>
-  <si>
-    <t>100Ω 5%</t>
-  </si>
-  <si>
-    <t>120Ω 5%</t>
-  </si>
-  <si>
-    <t>47Ω 5%</t>
-  </si>
-  <si>
-    <t>82Ω 5%</t>
-  </si>
-  <si>
-    <t>330Ω 5%</t>
-  </si>
-  <si>
-    <t>470KΩ 5%</t>
-  </si>
-  <si>
-    <t>100KΩ 5%</t>
-  </si>
-  <si>
-    <t>68Ω 5%</t>
-  </si>
-  <si>
-    <t>180Ω 5%</t>
-  </si>
-  <si>
-    <t>4.7KΩ 5%</t>
-  </si>
-  <si>
-    <t>1MΩ 5%</t>
-  </si>
-  <si>
-    <t>620Ω 5%</t>
-  </si>
-  <si>
-    <t>33KΩ 5%</t>
-  </si>
-  <si>
-    <t>360Ω 5%</t>
-  </si>
-  <si>
-    <t>39KΩ 5%</t>
-  </si>
-  <si>
-    <t>2.4KΩ 5%</t>
-  </si>
-  <si>
-    <t>3.9KΩ 5%</t>
-  </si>
-  <si>
-    <t>240Ω 5%</t>
-  </si>
-  <si>
-    <t>390Ω 5%</t>
-  </si>
-  <si>
-    <t>390Ω 1/2W 5%</t>
-  </si>
-  <si>
-    <t>3.3KΩ 5%</t>
-  </si>
-  <si>
-    <t>150Ω 5%</t>
-  </si>
-  <si>
-    <t>43KΩ 5%</t>
-  </si>
-  <si>
-    <t>470Ω 1/2W 5%</t>
-  </si>
-  <si>
-    <t>1KΩ</t>
-  </si>
-  <si>
-    <t>3.3KΩ</t>
-  </si>
-  <si>
-    <t>33Ω</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_68_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_390_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_110_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_47k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_560_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_10k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_1k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_100_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_120_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_47_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_82_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_330_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_470k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_100k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_180_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_4k7_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_1m_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_620_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_33k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_360_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_39k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_2k4_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_3k9_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_240_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_3k3_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_150_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_43k_5.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_470_5.png</t>
-  </si>
-  <si>
-    <t>29798145-14d2-4ccf-b284-666c1feecf11</t>
-  </si>
-  <si>
-    <t>0d47aa33-7e62-4406-95f3-9cacbe319b63</t>
-  </si>
-  <si>
-    <t>b4d41d84-ba61-49c6-a25c-3f7b2584c0cd</t>
-  </si>
-  <si>
-    <t>07d90e04-8d04-46d6-84bb-c7856875035c</t>
-  </si>
-  <si>
-    <t>9d3a62a1-cf47-48c0-bb76-ab07671c68f6</t>
-  </si>
-  <si>
-    <t>ad069483-3f80-47d5-813e-f82eb7b2294a</t>
-  </si>
-  <si>
-    <t>aca0b262-c348-4a93-8348-ce8ed11c981f</t>
-  </si>
-  <si>
-    <t>6f727b6f-dbfe-4549-9d65-0530f96c235e</t>
-  </si>
-  <si>
-    <t>fb34d637-a5da-4935-9846-3428ecd88469</t>
-  </si>
-  <si>
-    <t>6e8b3746-3474-4095-be41-56c0f610a1dd</t>
-  </si>
-  <si>
-    <t>634ef6e0-213d-4dc4-8964-8b5399e0fb26</t>
-  </si>
-  <si>
-    <t>1b77f300-27fe-46c7-9abb-401d941fe6b8</t>
-  </si>
-  <si>
-    <t>36232bd5-2100-42d4-9a9e-35d60fc21b37</t>
-  </si>
-  <si>
-    <t>c1c076d1-103c-4798-b109-1b8fca366a68</t>
-  </si>
-  <si>
-    <t>d959f284-7792-4696-8275-0f5df4914aaf</t>
-  </si>
-  <si>
-    <t>6a204d07-0623-4325-ba4f-436f32dcb452</t>
-  </si>
-  <si>
-    <t>12a2dc02-6fce-49c3-bb25-b3d9164c3581</t>
-  </si>
-  <si>
-    <t>fc80809f-7dee-42d9-a4ff-063f7cf81ea0</t>
-  </si>
-  <si>
-    <t>cad31e64-95f8-4008-94d5-3b6718317571</t>
-  </si>
-  <si>
-    <t>16d061b2-345a-40f4-9289-0e408f916b34</t>
-  </si>
-  <si>
-    <t>d4af3d2b-b01c-4025-aadd-e74ac62e52eb</t>
-  </si>
-  <si>
-    <t>f1c3c6fd-dfc2-4ca5-a026-24890e54e53f</t>
-  </si>
-  <si>
-    <t>6e9d74e4-3102-43eb-9932-7dc4b0b7b354</t>
-  </si>
-  <si>
-    <t>e01d6f1c-3122-40d5-8ddc-4f8543b3f3da</t>
-  </si>
-  <si>
-    <t>898f4a0e-b6fa-4919-bdf7-249e181d0ba4</t>
-  </si>
-  <si>
-    <t>3a3974f2-db9d-4d79-852f-a009b546203d</t>
-  </si>
-  <si>
-    <t>0a6e89db-2c6f-47fd-8755-16ada556f3ab</t>
-  </si>
-  <si>
-    <t>21bb9399-ab72-4b6f-a523-938ce3b159d3</t>
-  </si>
-  <si>
-    <t>129f8830-73ae-4097-95c1-ce56b6011acd</t>
-  </si>
-  <si>
-    <t>914762b7-8082-4996-b5f9-12704f06e762</t>
-  </si>
-  <si>
-    <t>1d56065a-9d40-4f9f-a09f-d67887fb857c</t>
-  </si>
-  <si>
-    <t>e1aadd5c-1184-4795-9dcc-727b1ab25eb2</t>
-  </si>
-  <si>
-    <t>d6a02eb8-31be-41ec-97c3-828e926ff0dc</t>
-  </si>
-  <si>
-    <t>fa7bfa12-105e-45c7-95aa-5c93daff310e</t>
-  </si>
-  <si>
-    <t>66f0cc67-61b9-4c62-a059-947748234941</t>
-  </si>
-  <si>
-    <t>d740ea45-df70-4eaa-8e38-9a7f5f6c349c</t>
-  </si>
-  <si>
-    <t>4b7bcfe3-59a4-4b88-8247-8feeb1fdaed8</t>
-  </si>
-  <si>
-    <t>cc2747d2-a929-442a-8c12-9d3785d97cfe</t>
-  </si>
-  <si>
-    <t>fbf87602-7d64-4180-931d-d62ebb231d37</t>
-  </si>
-  <si>
-    <t>590a2fe4-3a5f-427a-83a4-0e904ebc49e6</t>
-  </si>
-  <si>
-    <t>b9ba8087-fbfd-4110-a8e5-f086f5560d1a</t>
-  </si>
-  <si>
-    <t>75c56f71-1cc1-4b72-b777-911209ae1ca1</t>
-  </si>
-  <si>
-    <t>6562e03d-c7fa-4419-93a2-35a7bb734738</t>
-  </si>
-  <si>
-    <t>61bc7a87-98aa-4ab2-ba25-22ca71843846</t>
-  </si>
-  <si>
-    <t>5f3b4ab3-8784-43be-8e0e-ef823b36d6b0</t>
-  </si>
-  <si>
-    <t>882d16a3-4205-4279-b4ca-3e47b0a2fa04</t>
-  </si>
-  <si>
-    <t>101dc684-f2d3-4d40-a61a-c69e652ecc88</t>
-  </si>
-  <si>
-    <t>6847c8e3-2f19-4ef2-b09b-5ef1a4357680</t>
-  </si>
-  <si>
-    <t>a6bce5c0-50ed-4687-a397-17ddcbf3e093</t>
-  </si>
-  <si>
-    <t>21a9b69b-1507-4423-a54c-8d5023bf3207</t>
-  </si>
-  <si>
-    <t>c6728aa0-9114-4595-a78c-4eb95a382be2</t>
-  </si>
-  <si>
-    <t>dad7ff17-db1e-4adb-87e6-bbb99bc7bf9d</t>
-  </si>
-  <si>
-    <t>9fd79cb1-9ff9-48d8-9c3c-0f69b8449934</t>
-  </si>
-  <si>
-    <t>431209f3-c032-4698-a389-07d385161743</t>
-  </si>
-  <si>
-    <t>e463cc33-1480-4ef3-9be0-44a4986af536</t>
-  </si>
-  <si>
-    <t>be43dfc1-6ccb-447c-9bcc-3f28fd8dbd47</t>
-  </si>
-  <si>
-    <t>e2e4fefe-9401-40cc-840f-21d0c1d6b6d8</t>
-  </si>
-  <si>
-    <t>20a44421-fc33-4095-8509-447cacb2463f</t>
-  </si>
-  <si>
-    <t>ab04ae07-8963-452b-86a3-b5b8e60eead8</t>
-  </si>
-  <si>
-    <t>001f86a5-576d-4230-ac12-e56baa7232c3</t>
-  </si>
-  <si>
-    <t>47880fe2-bfd1-4422-80d0-7db3f1f061a6</t>
-  </si>
-  <si>
-    <t>fc266b91-84b3-4cfd-97ac-1c9d3d5be099</t>
-  </si>
-  <si>
-    <t>3b3ef4ce-31b3-46da-a0cc-291d9cd652a2</t>
-  </si>
-  <si>
-    <t>16a6db1c-fa1a-4d9f-9f5a-5e4c4108b918</t>
-  </si>
-  <si>
-    <t>1a35d386-4fbb-4e5e-8f73-5c73e8f8ff82</t>
-  </si>
-  <si>
-    <t>37805f44-f37a-428f-8f64-459cfd180a73</t>
-  </si>
-  <si>
-    <t>bbf7fb07-aeef-453c-a8b1-e5275a6bcd2f</t>
-  </si>
-  <si>
-    <t>5f5ca01f-ab6b-4723-9565-b54982d34722</t>
-  </si>
-  <si>
-    <t>48c8fc6e-a4b6-4d8f-9069-6117f26c870e</t>
-  </si>
-  <si>
-    <t>8df5b7c3-bc1a-4d08-8edc-02c6f06ff6b5</t>
-  </si>
-  <si>
-    <t>38fc59d4-8373-4c12-850b-adb1c3b1ec31</t>
-  </si>
-  <si>
-    <t>c90508a3-ce9f-4e96-bb7d-bafc4fa25316</t>
-  </si>
-  <si>
-    <t>40eba650-a94f-45de-806b-eb1030f475b0</t>
-  </si>
-  <si>
-    <t>c3d10f14-494c-4703-8046-1c29ea4de096</t>
-  </si>
-  <si>
-    <t>ee888045-cf15-478d-8e9c-a912842c5abb</t>
-  </si>
-  <si>
-    <t>730887f9-6873-4662-8306-bc35dd361f34</t>
-  </si>
-  <si>
-    <t>98d22239-bf38-4aa0-8390-f36671c0eb5e</t>
-  </si>
-  <si>
-    <t>d0093a48-8fa5-4a7b-8c11-092508336fce</t>
-  </si>
-  <si>
-    <t>c086072d-ebff-4e15-85b5-5f7c5f0a6c96</t>
-  </si>
-  <si>
-    <t>4ea9e23f-c7a0-4edb-8c2a-6d8d4dd637a6</t>
-  </si>
-  <si>
-    <t>00a390b5-b6d9-4377-8db5-5b4820f2cbb7</t>
-  </si>
-  <si>
-    <t>353eacc6-a22a-4eaa-8691-a18a17f628b8</t>
-  </si>
-  <si>
-    <t>24fee2b5-4fcf-470d-87ff-8debf57b8502</t>
-  </si>
-  <si>
-    <t>ee13a804-429f-41f1-bd99-af3eb450d714</t>
-  </si>
-  <si>
-    <t>fdda808a-7654-453c-93e3-964a7741e5cd</t>
-  </si>
-  <si>
-    <t>362cd708-dc4a-4428-a5fa-2817bb57f28f</t>
-  </si>
-  <si>
-    <t>b9bdfabb-4089-4ba7-81b5-4e0d76533c90</t>
-  </si>
-  <si>
-    <t>b20be889-01f9-460b-a931-864926851e41</t>
-  </si>
-  <si>
-    <t>bedc7acb-cfe1-4e58-bd90-52675b4b5b0b</t>
-  </si>
-  <si>
-    <t>4c45621c-a9eb-46ba-850a-2d740cb51969</t>
-  </si>
-  <si>
-    <t>741bd2da-a1db-409c-9ed0-0d5a473afee5</t>
-  </si>
-  <si>
-    <t>12719651-68eb-46a8-9704-9617da7ce814</t>
-  </si>
-  <si>
-    <t>6743bca1-3196-4d73-9d96-bc3e4dd6c187</t>
-  </si>
-  <si>
-    <t>629c2189-d625-497d-a096-cd382eeacfe2</t>
-  </si>
-  <si>
-    <t>5a06b6af-4d94-4e73-828d-5f1b3b352fc5</t>
-  </si>
-  <si>
-    <t>e0f5df0e-614b-49f0-9e18-c7c21aa944d5</t>
-  </si>
-  <si>
-    <t>7f000740-76ab-4a0c-b9f0-671508ba1347</t>
-  </si>
-  <si>
-    <t>d37ac297-d703-46c3-939b-e7e74c6aac10</t>
-  </si>
-  <si>
-    <t>c270834e-2802-4233-b494-fcbee9f726a8</t>
-  </si>
-  <si>
-    <t>081e7c90-1172-4764-9c1f-29880facca4b</t>
-  </si>
-  <si>
-    <t>f230237a-8761-4ba3-8502-ad63b838daa4</t>
-  </si>
-  <si>
-    <t>aff248a0-f3b9-4fe5-b7b1-cf3ea9839df0</t>
-  </si>
-  <si>
-    <t>03d34980-4390-4591-9f7a-bebfd61eeff7</t>
-  </si>
-  <si>
-    <t>b1d0dd12-0947-4c9c-8710-a06ba59d7b92</t>
-  </si>
-  <si>
-    <t>e1d0e5b1-92c1-4116-baf9-6d69d7148e87</t>
-  </si>
-  <si>
-    <t>9e520ffd-1c05-48ff-90b5-9db26a1a3c71</t>
-  </si>
-  <si>
-    <t>41705140-fc1b-40fd-96f0-609ad2a3e182</t>
-  </si>
-  <si>
-    <t>b5616c20-2c94-4876-91a8-52a405215c79</t>
-  </si>
-  <si>
-    <t>cd095f21-0ec6-418a-bc4c-4837a3e44b41</t>
-  </si>
-  <si>
-    <t>ce67d7d3-80d7-4147-9cc2-2f2ab522ec74</t>
-  </si>
-  <si>
-    <t>d664472d-653f-406d-b36a-560e22349873</t>
-  </si>
-  <si>
-    <t>33767dd7-c96c-4d86-9b38-a7eb6f6035b2</t>
-  </si>
-  <si>
-    <t>b51c9bd1-3f71-42b5-bc06-977d8cc6c1da</t>
-  </si>
-  <si>
-    <t>fb10526b-e91c-44e8-a471-a9f298393b14</t>
-  </si>
-  <si>
-    <t>1275beac-ed3c-4064-b6b3-a34f8eaf0e51</t>
-  </si>
-  <si>
-    <t>696baa4e-0d8c-4347-be27-4562e3c015a9</t>
-  </si>
-  <si>
-    <t>4ce0f8ba-1794-41d2-a70c-95235c80ca4d</t>
-  </si>
-  <si>
-    <t>d1251977-0da4-4e1f-a6d6-101e743a4393</t>
-  </si>
-  <si>
-    <t>7e107c40-854b-4b4a-9d33-d829a077427f</t>
-  </si>
-  <si>
-    <t>b440d249-a9f8-407d-872b-589b749d49e4</t>
-  </si>
-  <si>
-    <t>7ef3a38f-83bf-40d3-8660-6c93c59e1645</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/C128 Keyboard matrix.png</t>
-  </si>
-  <si>
-    <t>Keyboard matrix</t>
-  </si>
-  <si>
-    <t>382eabc1-db16-4658-8b8d-ba2966fe0f95</t>
-  </si>
-  <si>
-    <t>Resistor pack, 8 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 6 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 9 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 7 pin</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_pack_8pin.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_pack_7pin.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_pack_9pin.png</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component images/resistor_pack_6pin.png</t>
-  </si>
-  <si>
-    <t>9e2b8f16-82c7-4493-8cc8-4f1a71ca060a</t>
-  </si>
-  <si>
-    <t>b433bc07-19eb-402d-a7b6-786d716cb800</t>
-  </si>
-  <si>
-    <t>3b9f0451-1436-4784-b9d0-9a9b73fa6638</t>
-  </si>
-  <si>
-    <t>13a7828d-5627-4526-b418-fd21e9accc13</t>
-  </si>
-  <si>
-    <t>c3663a71-1852-4713-946e-5b0192088944</t>
-  </si>
-  <si>
-    <t>d81bb017-423c-46fe-afd1-6c36fda03e70</t>
-  </si>
-  <si>
-    <t>e595386d-a3ff-4d0a-9c7e-52b84ee60ff5</t>
-  </si>
-  <si>
-    <t>c096fc45-a4eb-4486-8e16-110ebcfb2bde</t>
-  </si>
-  <si>
-    <t>fc426b09-ae14-415c-a668-fd777dce0aef</t>
-  </si>
-  <si>
-    <t>Resistor packs must be mounted with GND pin at its designated position</t>
   </si>
 </sst>
 </file>
@@ -6502,7 +6588,7 @@
     </row>
     <row r="3" spans="1:18" s="10" customFormat="1" ht="21">
       <c r="A3" s="10" t="s">
-        <v>1681</v>
+        <v>1915</v>
       </c>
       <c r="H3" s="59"/>
       <c r="I3" s="59"/>
@@ -12376,7 +12462,7 @@
         <v>410</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>683</v>
@@ -12390,7 +12476,7 @@
         <v>429</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>683</v>
@@ -12404,7 +12490,7 @@
         <v>461</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>683</v>
@@ -12418,7 +12504,7 @@
         <v>449</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>683</v>
@@ -12432,7 +12518,7 @@
         <v>460</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>683</v>
@@ -12446,7 +12532,7 @@
         <v>428</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>683</v>
@@ -12460,7 +12546,7 @@
         <v>452</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>683</v>
@@ -12474,7 +12560,7 @@
         <v>450</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>683</v>
@@ -12522,7 +12608,7 @@
         <v>403</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>683</v>
@@ -12536,7 +12622,7 @@
         <v>423</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>683</v>
@@ -12550,7 +12636,7 @@
         <v>413</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>683</v>
@@ -12564,7 +12650,7 @@
         <v>414</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>683</v>
@@ -12578,7 +12664,7 @@
         <v>421</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>683</v>
@@ -12592,7 +12678,7 @@
         <v>458</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>683</v>
@@ -12606,7 +12692,7 @@
         <v>453</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>683</v>
@@ -12620,7 +12706,7 @@
         <v>455</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>683</v>
@@ -12634,7 +12720,7 @@
         <v>464</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>683</v>
@@ -12648,7 +12734,7 @@
         <v>454</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>683</v>
@@ -12662,7 +12748,7 @@
         <v>451</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>683</v>
@@ -12676,7 +12762,7 @@
         <v>422</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>683</v>
@@ -12690,7 +12776,7 @@
         <v>689</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>683</v>
@@ -12704,7 +12790,7 @@
         <v>407</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>683</v>
@@ -12718,7 +12804,7 @@
         <v>409</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>683</v>
@@ -12732,7 +12818,7 @@
         <v>466</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>683</v>
@@ -12746,7 +12832,7 @@
         <v>427</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>683</v>
@@ -12760,7 +12846,7 @@
         <v>424</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>683</v>
@@ -12774,7 +12860,7 @@
         <v>612</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>683</v>
@@ -12788,7 +12874,7 @@
         <v>597</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>683</v>
@@ -12819,7 +12905,7 @@
         <v>658</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>683</v>
@@ -12833,7 +12919,7 @@
         <v>629</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>683</v>
@@ -12847,7 +12933,7 @@
         <v>636</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>683</v>
@@ -12861,7 +12947,7 @@
         <v>637</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>683</v>
@@ -12875,7 +12961,7 @@
         <v>638</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>683</v>
@@ -12889,7 +12975,7 @@
         <v>645</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>683</v>
@@ -12903,7 +12989,7 @@
         <v>641</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>683</v>
@@ -12934,7 +13020,7 @@
         <v>682</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>683</v>
@@ -12948,7 +13034,7 @@
         <v>647</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>683</v>
@@ -12962,7 +13048,7 @@
         <v>652</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>683</v>
@@ -12993,7 +13079,7 @@
         <v>651</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>683</v>
@@ -13007,7 +13093,7 @@
         <v>649</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>683</v>
@@ -13021,7 +13107,7 @@
         <v>667</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>683</v>
@@ -13035,7 +13121,7 @@
         <v>672</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>683</v>
@@ -13049,7 +13135,7 @@
         <v>673</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>683</v>
@@ -13063,7 +13149,7 @@
         <v>678</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>683</v>
@@ -13077,7 +13163,7 @@
         <v>679</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>683</v>
@@ -13091,7 +13177,7 @@
         <v>681</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>683</v>
@@ -13105,7 +13191,7 @@
         <v>680</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>683</v>
@@ -13119,7 +13205,7 @@
         <v>661</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>683</v>
@@ -13133,7 +13219,7 @@
         <v>655</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>683</v>
@@ -13147,7 +13233,7 @@
         <v>654</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>683</v>
@@ -13161,7 +13247,7 @@
         <v>662</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>683</v>
@@ -13175,7 +13261,7 @@
         <v>705</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>683</v>
@@ -13192,7 +13278,7 @@
         <v>716</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>683</v>
@@ -13209,7 +13295,7 @@
         <v>567</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>683</v>
@@ -13223,7 +13309,7 @@
         <v>568</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>683</v>
@@ -13237,7 +13323,7 @@
         <v>560</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>683</v>
@@ -13285,7 +13371,7 @@
         <v>633</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>683</v>
@@ -13299,13 +13385,13 @@
         <v>404</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H378" t="s">
         <v>1248</v>
@@ -13316,13 +13402,13 @@
         <v>456</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H379" t="s">
         <v>1249</v>
@@ -13333,13 +13419,13 @@
         <v>408</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H380" t="s">
         <v>1250</v>
@@ -13350,13 +13436,13 @@
         <v>406</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H381" t="s">
         <v>1251</v>
@@ -13367,13 +13453,13 @@
         <v>457</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H382" t="s">
         <v>1252</v>
@@ -13384,13 +13470,13 @@
         <v>405</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H383" t="s">
         <v>1253</v>
@@ -13401,13 +13487,13 @@
         <v>426</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H384" t="s">
         <v>1254</v>
@@ -13418,13 +13504,13 @@
         <v>430</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H385" t="s">
         <v>1255</v>
@@ -13435,13 +13521,13 @@
         <v>624</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H386" t="s">
         <v>1256</v>
@@ -13694,7 +13780,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L2922"/>
+  <dimension ref="A1:L2945"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -16731,13 +16817,13 @@
         <v>722</v>
       </c>
       <c r="I171" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="J171" s="1" t="s">
         <v>1867</v>
       </c>
-      <c r="J171" s="1" t="s">
+      <c r="K171" t="s">
         <v>1868</v>
-      </c>
-      <c r="K171" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -17493,7 +17579,7 @@
         <v>1614</v>
       </c>
       <c r="K221" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -17769,7 +17855,7 @@
         <v>822</v>
       </c>
       <c r="K238" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -17820,22 +17906,19 @@
       </c>
     </row>
     <row r="242" spans="1:11">
-      <c r="A242" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B242" s="13"/>
-      <c r="C242" s="49"/>
+      <c r="A242" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B242" s="11"/>
+      <c r="C242" s="50"/>
       <c r="D242" s="11" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I242" s="11" t="s">
-        <v>836</v>
-      </c>
-      <c r="J242" s="1" t="s">
-        <v>837</v>
+        <v>1887</v>
       </c>
       <c r="K242" t="s">
-        <v>1467</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -17845,46 +17928,51 @@
       <c r="B243" s="13"/>
       <c r="C243" s="49"/>
       <c r="D243" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I243" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="K243" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B244" s="13"/>
+      <c r="C244" s="49"/>
+      <c r="D244" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="I243" s="11" t="s">
+      <c r="I244" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="K243" t="s">
+      <c r="K244" t="s">
         <v>1468</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11">
-      <c r="A244" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I244" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="K244" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="1" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>839</v>
+        <v>1645</v>
       </c>
       <c r="K245" t="s">
-        <v>1469</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>722</v>
@@ -17893,40 +17981,35 @@
         <v>839</v>
       </c>
       <c r="K246" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I247" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="K247" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11">
+      <c r="A248" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I248" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="K247" t="s">
+      <c r="K248" t="s">
         <v>1471</v>
-      </c>
-    </row>
-    <row r="248" spans="1:11">
-      <c r="A248" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B248" s="13"/>
-      <c r="C248" s="49"/>
-      <c r="D248" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I248" s="11" t="s">
-        <v>836</v>
-      </c>
-      <c r="J248" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="K248" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -17936,35 +18019,37 @@
       <c r="B249" s="13"/>
       <c r="C249" s="49"/>
       <c r="D249" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I249" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="K249" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11">
+      <c r="A250" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B250" s="13"/>
+      <c r="C250" s="49"/>
+      <c r="D250" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="I249" s="11" t="s">
+      <c r="I250" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="K249" t="s">
+      <c r="K250" t="s">
         <v>1473</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11">
-      <c r="A250" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="I250" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="J250" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="K250" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>722</v>
@@ -17976,12 +18061,12 @@
         <v>713</v>
       </c>
       <c r="K251" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>722</v>
@@ -17993,12 +18078,12 @@
         <v>713</v>
       </c>
       <c r="K252" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="253" spans="1:11">
       <c r="A253" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>722</v>
@@ -18010,21 +18095,24 @@
         <v>713</v>
       </c>
       <c r="K253" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>821</v>
+        <v>832</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>713</v>
       </c>
       <c r="K254" t="s">
-        <v>1641</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -18032,41 +18120,41 @@
         <v>109</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>1638</v>
+        <v>821</v>
       </c>
       <c r="K255" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>803</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1647</v>
+        <v>1638</v>
       </c>
       <c r="K256" t="s">
-        <v>1478</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="1" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>842</v>
+        <v>1647</v>
       </c>
       <c r="K257" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -18074,27 +18162,27 @@
         <v>68</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>1610</v>
+        <v>842</v>
       </c>
       <c r="K258" t="s">
-        <v>1612</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="1" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>843</v>
+        <v>1610</v>
       </c>
       <c r="K259" t="s">
-        <v>1480</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -18102,29 +18190,27 @@
         <v>111</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>1648</v>
+        <v>843</v>
       </c>
       <c r="K260" t="s">
-        <v>1649</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B261" s="11"/>
-      <c r="C261" s="50"/>
-      <c r="D261" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I261" s="11" t="s">
-        <v>1650</v>
+        <v>111</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>1648</v>
       </c>
       <c r="K261" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -18134,27 +18220,29 @@
       <c r="B262" s="11"/>
       <c r="C262" s="50"/>
       <c r="D262" s="11" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I262" s="11" t="s">
-        <v>1651</v>
-      </c>
-      <c r="K262" s="57" t="s">
-        <v>1653</v>
+        <v>1650</v>
+      </c>
+      <c r="K262" t="s">
+        <v>1652</v>
       </c>
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="I263" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="K263" t="s">
-        <v>1481</v>
+        <v>69</v>
+      </c>
+      <c r="B263" s="11"/>
+      <c r="C263" s="50"/>
+      <c r="D263" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="I263" s="11" t="s">
+        <v>1651</v>
+      </c>
+      <c r="K263" s="57" t="s">
+        <v>1653</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -18162,41 +18250,41 @@
         <v>70</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>1654</v>
+        <v>844</v>
       </c>
       <c r="K264" t="s">
-        <v>1655</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>803</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>1680</v>
+        <v>1654</v>
       </c>
       <c r="K265" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="1" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>844</v>
+        <v>1680</v>
       </c>
       <c r="K266" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -18204,32 +18292,27 @@
         <v>71</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>1654</v>
+        <v>844</v>
       </c>
       <c r="K267" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B268" s="11"/>
-      <c r="C268" s="50"/>
-      <c r="D268" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I268" s="11" t="s">
-        <v>1665</v>
-      </c>
-      <c r="J268" s="1" t="s">
-        <v>816</v>
+        <v>71</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>1654</v>
       </c>
       <c r="K268" t="s">
-        <v>1669</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -18239,32 +18322,32 @@
       <c r="B269" s="11"/>
       <c r="C269" s="50"/>
       <c r="D269" s="11" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I269" s="11" t="s">
-        <v>1666</v>
+        <v>1665</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>816</v>
       </c>
       <c r="K269" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B270" s="13"/>
-      <c r="C270" s="49"/>
+        <v>72</v>
+      </c>
+      <c r="B270" s="11"/>
+      <c r="C270" s="50"/>
       <c r="D270" s="11" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I270" s="11" t="s">
-        <v>836</v>
-      </c>
-      <c r="J270" s="1" t="s">
-        <v>837</v>
+        <v>1666</v>
       </c>
       <c r="K270" t="s">
-        <v>1482</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -18274,161 +18357,166 @@
       <c r="B271" s="13"/>
       <c r="C271" s="49"/>
       <c r="D271" s="11" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I271" s="11" t="s">
-        <v>838</v>
+        <v>836</v>
+      </c>
+      <c r="J271" s="1" t="s">
+        <v>837</v>
       </c>
       <c r="K271" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="1" t="s">
-        <v>625</v>
+        <v>115</v>
       </c>
       <c r="B272" s="13"/>
       <c r="C272" s="49"/>
       <c r="D272" s="11" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I272" s="11" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="K272" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D273" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B273" s="13"/>
+      <c r="C273" s="49"/>
+      <c r="D273" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I273" s="1" t="s">
-        <v>839</v>
+      <c r="I273" s="11" t="s">
+        <v>845</v>
       </c>
       <c r="K273" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="K274" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="K275" t="s">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" ht="57.6">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11">
       <c r="A276" s="1" t="s">
-        <v>631</v>
+        <v>482</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="J276" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="K276" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" ht="57.6">
       <c r="A277" s="1" t="s">
-        <v>484</v>
+        <v>631</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>848</v>
       </c>
       <c r="K277" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="K278" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="J279" s="1" t="s">
-        <v>769</v>
+        <v>849</v>
       </c>
       <c r="K279" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>769</v>
       </c>
       <c r="K280" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="1" t="s">
-        <v>656</v>
+        <v>489</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K281" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -18436,46 +18524,41 @@
         <v>656</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1659</v>
+        <v>852</v>
       </c>
       <c r="K282" t="s">
-        <v>1660</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>803</v>
       </c>
       <c r="I283" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="K283" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11">
+      <c r="A284" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I284" s="1" t="s">
         <v>1661</v>
       </c>
-      <c r="K283" t="s">
+      <c r="K284" t="s">
         <v>1494</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11">
-      <c r="A284" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B284" s="13"/>
-      <c r="C284" s="49"/>
-      <c r="D284" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I284" s="11" t="s">
-        <v>836</v>
-      </c>
-      <c r="J284" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -18485,27 +18568,32 @@
       <c r="B285" s="13"/>
       <c r="C285" s="49"/>
       <c r="D285" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I285" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="K285" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11">
+      <c r="A286" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B286" s="13"/>
+      <c r="C286" s="49"/>
+      <c r="D286" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="I285" s="11" t="s">
+      <c r="I286" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="K285" t="s">
+      <c r="K286" t="s">
         <v>1496</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11">
-      <c r="A286" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="I286" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -18513,27 +18601,27 @@
         <v>628</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1619</v>
+        <v>823</v>
       </c>
       <c r="K287" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>823</v>
+        <v>1619</v>
       </c>
       <c r="K288" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -18541,748 +18629,777 @@
         <v>626</v>
       </c>
       <c r="D289" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="K289" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11">
+      <c r="A290" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I289" s="1" t="s">
+      <c r="I290" s="1" t="s">
         <v>1619</v>
       </c>
-      <c r="K289" t="s">
+      <c r="K290" t="s">
         <v>1625</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11">
-      <c r="A290" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="B290" s="11"/>
-      <c r="C290" s="50"/>
-      <c r="D290" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I290" s="11" t="s">
-        <v>853</v>
-      </c>
-      <c r="J290" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1497</v>
       </c>
     </row>
     <row r="291" spans="1:11" ht="72">
       <c r="A291" s="1" t="s">
-        <v>238</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="J291" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="K291" t="s">
-        <v>1498</v>
+      <c r="H291"/>
+      <c r="I291" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="J291" s="30" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K291" s="1" t="s">
+        <v>1910</v>
       </c>
     </row>
     <row r="292" spans="1:11" ht="72">
       <c r="A292" s="1" t="s">
-        <v>240</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="J292" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="K292" t="s">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11">
-      <c r="A293" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="B293" s="13"/>
-      <c r="C293" s="49"/>
-      <c r="D293" s="11" t="s">
+      <c r="H292"/>
+      <c r="I292" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="J292" s="30" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K292" s="1" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" ht="72">
+      <c r="A293" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="I293" s="11" t="s">
-        <v>1718</v>
-      </c>
-      <c r="J293" s="30"/>
-      <c r="K293" s="57" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" ht="28.8">
+      <c r="H293"/>
+      <c r="I293" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="J293" s="30" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K293" s="1" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" ht="57.6">
       <c r="A294" s="1" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C294" s="1"/>
-      <c r="D294" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I294" s="11" t="s">
-        <v>856</v>
+      <c r="D294" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H294"/>
+      <c r="I294" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J294" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K294" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K294" s="1" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" ht="57.6">
       <c r="A295" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B295" s="13"/>
-      <c r="C295" s="49"/>
+        <v>438</v>
+      </c>
+      <c r="C295" s="1"/>
       <c r="D295" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I295" s="11" t="s">
-        <v>1719</v>
-      </c>
-      <c r="J295" s="30"/>
-      <c r="K295" s="57" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" ht="28.8">
+      <c r="H295"/>
+      <c r="I295" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J295" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K295" s="1" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" ht="57.6">
       <c r="A296" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C296" s="1"/>
-      <c r="D296" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I296" s="11" t="s">
-        <v>856</v>
+      <c r="D296" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H296"/>
+      <c r="I296" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J296" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K296" s="1" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" ht="57.6">
       <c r="A297" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="B297" s="13"/>
-      <c r="C297" s="49"/>
+        <v>436</v>
+      </c>
+      <c r="C297" s="1"/>
       <c r="D297" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I297" s="11" t="s">
-        <v>1720</v>
-      </c>
-      <c r="J297" s="30"/>
-      <c r="K297" s="57" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" ht="28.8">
+      <c r="H297"/>
+      <c r="I297" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J297" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K297" s="58" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" ht="57.6">
       <c r="A298" s="1" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="C298" s="1"/>
-      <c r="D298" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I298" s="11" t="s">
-        <v>856</v>
+      <c r="D298" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H298"/>
+      <c r="I298" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J298" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K298" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K298" s="1" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" ht="57.6">
       <c r="A299" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B299" s="13"/>
-      <c r="C299" s="49"/>
+        <v>432</v>
+      </c>
+      <c r="C299" s="1"/>
       <c r="D299" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I299" s="11" t="s">
-        <v>1721</v>
-      </c>
-      <c r="J299" s="30"/>
-      <c r="K299" s="57" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="300" spans="1:11" ht="28.8">
+      <c r="H299"/>
+      <c r="I299" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J299" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K299" s="1" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" ht="57.6">
       <c r="A300" s="1" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C300" s="1"/>
-      <c r="D300" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I300" s="11" t="s">
-        <v>856</v>
+      <c r="D300" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H300"/>
+      <c r="I300" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J300" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K300" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="301" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K300" s="1" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" ht="57.6">
       <c r="A301" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B301" s="13"/>
-      <c r="C301" s="49"/>
+        <v>420</v>
+      </c>
+      <c r="C301" s="1"/>
       <c r="D301" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I301" s="11" t="s">
-        <v>1722</v>
-      </c>
-      <c r="J301" s="30"/>
-      <c r="K301" s="57" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="302" spans="1:11" ht="28.8">
+      <c r="H301"/>
+      <c r="I301" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J301" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K301" s="1" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" ht="57.6">
       <c r="A302" s="1" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="C302" s="1"/>
-      <c r="D302" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I302" s="11" t="s">
-        <v>856</v>
+      <c r="D302" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H302"/>
+      <c r="I302" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J302" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K302" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K302" s="1" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" ht="57.6">
       <c r="A303" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B303" s="13"/>
-      <c r="C303" s="49"/>
+        <v>418</v>
+      </c>
+      <c r="C303" s="1"/>
       <c r="D303" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I303" s="11" t="s">
-        <v>1723</v>
-      </c>
-      <c r="J303" s="30"/>
-      <c r="K303" s="57" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="304" spans="1:11" ht="28.8">
+      <c r="H303"/>
+      <c r="I303" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J303" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K303" s="1" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" ht="57.6">
       <c r="A304" s="1" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C304" s="1"/>
-      <c r="D304" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I304" s="11" t="s">
-        <v>856</v>
+      <c r="D304" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H304"/>
+      <c r="I304" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J304" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K304" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K304" s="1" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" ht="57.6">
       <c r="A305" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="B305" s="13"/>
-      <c r="C305" s="49"/>
+        <v>616</v>
+      </c>
+      <c r="C305" s="1"/>
       <c r="D305" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I305" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J305" s="30"/>
-      <c r="K305" s="57" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" ht="28.8">
+      <c r="H305"/>
+      <c r="I305" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J305" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K305" s="1" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" ht="57.6">
       <c r="A306" s="1" t="s">
-        <v>452</v>
+        <v>617</v>
       </c>
       <c r="C306" s="1"/>
-      <c r="D306" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I306" s="11" t="s">
-        <v>856</v>
+      <c r="D306" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H306"/>
+      <c r="I306" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J306" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K306" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K306" s="1" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" ht="57.6">
       <c r="A307" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="B307" s="13"/>
-      <c r="C307" s="49"/>
+        <v>618</v>
+      </c>
+      <c r="C307" s="1"/>
       <c r="D307" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I307" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J307" s="30"/>
-      <c r="K307" s="57" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" ht="28.8">
+      <c r="H307"/>
+      <c r="I307" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J307" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" ht="57.6">
       <c r="A308" s="1" t="s">
-        <v>450</v>
+        <v>619</v>
       </c>
       <c r="C308" s="1"/>
-      <c r="D308" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I308" s="11" t="s">
-        <v>856</v>
+      <c r="D308" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H308"/>
+      <c r="I308" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J308" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K308" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" ht="28.8">
+        <v>1914</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" ht="57.6">
       <c r="A309" s="1" t="s">
-        <v>684</v>
+        <v>620</v>
       </c>
       <c r="C309" s="1"/>
-      <c r="D309" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I309" s="11" t="s">
-        <v>856</v>
+      <c r="D309" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H309"/>
+      <c r="I309" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J309" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K309" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" ht="28.8">
+        <v>1914</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" ht="57.6">
       <c r="A310" s="1" t="s">
-        <v>685</v>
+        <v>621</v>
       </c>
       <c r="C310" s="1"/>
-      <c r="D310" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I310" s="11" t="s">
-        <v>856</v>
+      <c r="D310" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H310"/>
+      <c r="I310" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J310" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K310" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11">
+        <v>1914</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" ht="57.6">
       <c r="A311" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B311" s="13"/>
-      <c r="C311" s="49"/>
+        <v>622</v>
+      </c>
+      <c r="C311" s="1"/>
       <c r="D311" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I311" s="11" t="s">
-        <v>1725</v>
-      </c>
-      <c r="J311" s="30"/>
-      <c r="K311" s="57" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" ht="28.8">
+      <c r="H311"/>
+      <c r="I311" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J311" s="30" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" ht="57.6">
       <c r="A312" s="1" t="s">
-        <v>403</v>
+        <v>694</v>
       </c>
       <c r="C312" s="1"/>
-      <c r="D312" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I312" s="11" t="s">
-        <v>856</v>
+      <c r="D312" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H312"/>
+      <c r="I312" s="1" t="s">
+        <v>1889</v>
       </c>
       <c r="J312" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K312" t="s">
-        <v>1765</v>
+        <v>1914</v>
+      </c>
+      <c r="K312" s="1" t="s">
+        <v>1908</v>
       </c>
     </row>
     <row r="313" spans="1:11">
-      <c r="A313" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B313" s="13"/>
-      <c r="C313" s="49"/>
+      <c r="A313" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="B313" s="11"/>
+      <c r="C313" s="50"/>
       <c r="D313" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I313" s="11" t="s">
-        <v>1726</v>
-      </c>
-      <c r="J313" s="30"/>
-      <c r="K313" s="57" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11" ht="28.8">
+        <v>853</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="K313" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" ht="72">
       <c r="A314" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C314" s="1"/>
+        <v>238</v>
+      </c>
       <c r="D314" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J314" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="K314" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" ht="72">
+      <c r="A315" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="K315" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11">
+      <c r="A316" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="B316" s="13"/>
+      <c r="C316" s="49"/>
+      <c r="D316" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I316" s="11" t="s">
+        <v>1717</v>
+      </c>
+      <c r="J316" s="30"/>
+      <c r="K316" s="57" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" ht="28.8">
+      <c r="A317" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I314" s="11" t="s">
+      <c r="I317" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J314" s="30" t="s">
+      <c r="J317" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K314" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11">
-      <c r="A315" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B315" s="13"/>
-      <c r="C315" s="49"/>
-      <c r="D315" s="11" t="s">
+      <c r="K317" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11">
+      <c r="A318" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B318" s="13"/>
+      <c r="C318" s="49"/>
+      <c r="D318" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I315" s="11" t="s">
-        <v>1727</v>
-      </c>
-      <c r="J315" s="30"/>
-      <c r="K315" s="57" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11" ht="28.8">
-      <c r="A316" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C316" s="1"/>
-      <c r="D316" s="1" t="s">
+      <c r="I318" s="11" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J318" s="30"/>
+      <c r="K318" s="57" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" ht="28.8">
+      <c r="A319" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I316" s="11" t="s">
+      <c r="I319" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J316" s="30" t="s">
+      <c r="J319" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K316" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11">
-      <c r="A317" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B317" s="13"/>
-      <c r="C317" s="49"/>
-      <c r="D317" s="11" t="s">
+      <c r="K319" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11">
+      <c r="A320" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B320" s="13"/>
+      <c r="C320" s="49"/>
+      <c r="D320" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I317" s="11" t="s">
-        <v>1728</v>
-      </c>
-      <c r="J317" s="30"/>
-      <c r="K317" s="57" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11" ht="28.8">
-      <c r="A318" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C318" s="1"/>
-      <c r="D318" s="1" t="s">
+      <c r="I320" s="11" t="s">
+        <v>1719</v>
+      </c>
+      <c r="J320" s="30"/>
+      <c r="K320" s="57" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" ht="28.8">
+      <c r="A321" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I318" s="11" t="s">
+      <c r="I321" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J318" s="30" t="s">
+      <c r="J321" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K318" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11">
-      <c r="A319" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B319" s="13"/>
-      <c r="C319" s="49"/>
-      <c r="D319" s="11" t="s">
+      <c r="K321" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11">
+      <c r="A322" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B322" s="13"/>
+      <c r="C322" s="49"/>
+      <c r="D322" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I319" s="11" t="s">
-        <v>1729</v>
-      </c>
-      <c r="J319" s="30"/>
-      <c r="K319" s="57" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11" ht="28.8">
-      <c r="A320" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1" t="s">
+      <c r="I322" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J322" s="30"/>
+      <c r="K322" s="57" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" ht="28.8">
+      <c r="A323" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I320" s="11" t="s">
+      <c r="I323" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J320" s="30" t="s">
+      <c r="J323" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K320" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11">
-      <c r="A321" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="B321" s="13"/>
-      <c r="C321" s="49"/>
-      <c r="D321" s="11" t="s">
+      <c r="K323" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11">
+      <c r="A324" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B324" s="13"/>
+      <c r="C324" s="49"/>
+      <c r="D324" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I321" s="11" t="s">
+      <c r="I324" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="J324" s="30"/>
+      <c r="K324" s="57" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" ht="28.8">
+      <c r="A325" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I325" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J325" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K325" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11">
+      <c r="A326" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B326" s="13"/>
+      <c r="C326" s="49"/>
+      <c r="D326" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I326" s="11" t="s">
+        <v>1722</v>
+      </c>
+      <c r="J326" s="30"/>
+      <c r="K326" s="57" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" ht="28.8">
+      <c r="A327" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I327" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J327" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K327" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11">
+      <c r="A328" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B328" s="13"/>
+      <c r="C328" s="49"/>
+      <c r="D328" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I328" s="11" t="s">
         <v>1723</v>
       </c>
-      <c r="J321" s="30"/>
-      <c r="K321" s="57" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11" ht="28.8">
-      <c r="A322" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1" t="s">
+      <c r="J328" s="30"/>
+      <c r="K328" s="57" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" ht="28.8">
+      <c r="A329" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I322" s="11" t="s">
+      <c r="I329" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J322" s="30" t="s">
+      <c r="J329" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K322" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11">
-      <c r="A323" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B323" s="13"/>
-      <c r="C323" s="49"/>
-      <c r="D323" s="11" t="s">
+      <c r="K329" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11">
+      <c r="A330" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B330" s="13"/>
+      <c r="C330" s="49"/>
+      <c r="D330" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I323" s="11" t="s">
-        <v>1730</v>
-      </c>
-      <c r="J323" s="30"/>
-      <c r="K323" s="57" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11" ht="28.8">
-      <c r="A324" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C324" s="1"/>
-      <c r="D324" s="1" t="s">
+      <c r="I330" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J330" s="30"/>
+      <c r="K330" s="57" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" ht="28.8">
+      <c r="A331" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I324" s="11" t="s">
+      <c r="I331" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J324" s="30" t="s">
+      <c r="J331" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K324" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11">
-      <c r="A325" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="B325" s="13"/>
-      <c r="C325" s="49"/>
-      <c r="D325" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I325" s="11" t="s">
-        <v>1721</v>
-      </c>
-      <c r="J325" s="30"/>
-      <c r="K325" s="57" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11" ht="28.8">
-      <c r="A326" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C326" s="1"/>
-      <c r="D326" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I326" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J326" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K326" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11">
-      <c r="A327" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B327" s="13"/>
-      <c r="C327" s="49"/>
-      <c r="D327" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I327" s="11" t="s">
-        <v>1731</v>
-      </c>
-      <c r="J327" s="30"/>
-      <c r="K327" s="57" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11" ht="28.8">
-      <c r="A328" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C328" s="1"/>
-      <c r="D328" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I328" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J328" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K328" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11">
-      <c r="A329" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B329" s="13"/>
-      <c r="C329" s="49"/>
-      <c r="D329" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I329" s="11" t="s">
-        <v>1721</v>
-      </c>
-      <c r="J329" s="30"/>
-      <c r="K329" s="57" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11" ht="28.8">
-      <c r="A330" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C330" s="1"/>
-      <c r="D330" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I330" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J330" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K330" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11">
-      <c r="A331" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="B331" s="13"/>
-      <c r="C331" s="49"/>
-      <c r="D331" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I331" s="11" t="s">
-        <v>1731</v>
-      </c>
-      <c r="J331" s="30"/>
-      <c r="K331" s="57" t="s">
-        <v>1784</v>
+      <c r="K331" t="s">
+        <v>1760</v>
       </c>
     </row>
     <row r="332" spans="1:11" ht="28.8">
       <c r="A332" s="1" t="s">
-        <v>451</v>
+        <v>684</v>
       </c>
       <c r="C332" s="1"/>
       <c r="D332" s="1" t="s">
@@ -19295,331 +19412,331 @@
         <v>857</v>
       </c>
       <c r="K332" t="s">
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="333" spans="1:11">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" ht="28.8">
       <c r="A333" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B333" s="13"/>
-      <c r="C333" s="49"/>
-      <c r="D333" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I333" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J333" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K333" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11">
+      <c r="A334" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B334" s="13"/>
+      <c r="C334" s="49"/>
+      <c r="D334" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I333" s="11" t="s">
+      <c r="I334" s="11" t="s">
+        <v>1724</v>
+      </c>
+      <c r="J334" s="30"/>
+      <c r="K334" s="57" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" ht="28.8">
+      <c r="A335" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I335" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J335" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11">
+      <c r="A336" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B336" s="13"/>
+      <c r="C336" s="49"/>
+      <c r="D336" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I336" s="11" t="s">
         <v>1725</v>
       </c>
-      <c r="J333" s="30"/>
-      <c r="K333" s="57" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="334" spans="1:11" ht="28.8">
-      <c r="A334" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C334" s="1"/>
-      <c r="D334" s="1" t="s">
+      <c r="J336" s="30"/>
+      <c r="K336" s="57" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" ht="28.8">
+      <c r="A337" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I334" s="11" t="s">
+      <c r="I337" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J334" s="30" t="s">
+      <c r="J337" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K334" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="335" spans="1:11">
-      <c r="A335" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="B335" s="13"/>
-      <c r="C335" s="49"/>
-      <c r="D335" s="11" t="s">
+      <c r="K337" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11">
+      <c r="A338" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B338" s="13"/>
+      <c r="C338" s="49"/>
+      <c r="D338" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I335" s="11" t="s">
-        <v>1723</v>
-      </c>
-      <c r="J335" s="30"/>
-      <c r="K335" s="57" t="s">
-        <v>1788</v>
-      </c>
-    </row>
-    <row r="336" spans="1:11" ht="28.8">
-      <c r="A336" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C336" s="1"/>
-      <c r="D336" s="1" t="s">
+      <c r="I338" s="11" t="s">
+        <v>1726</v>
+      </c>
+      <c r="J338" s="30"/>
+      <c r="K338" s="57" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" ht="28.8">
+      <c r="A339" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I336" s="11" t="s">
+      <c r="I339" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J336" s="30" t="s">
+      <c r="J339" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K336" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11">
-      <c r="A337" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B337" s="13"/>
-      <c r="C337" s="49"/>
-      <c r="D337" s="11" t="s">
+      <c r="K339" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11">
+      <c r="A340" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B340" s="13"/>
+      <c r="C340" s="49"/>
+      <c r="D340" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I337" s="11" t="s">
-        <v>1718</v>
-      </c>
-      <c r="J337" s="30"/>
-      <c r="K337" s="57" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="338" spans="1:11" ht="28.8">
-      <c r="A338" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C338" s="1"/>
-      <c r="D338" s="1" t="s">
+      <c r="I340" s="11" t="s">
+        <v>1727</v>
+      </c>
+      <c r="J340" s="30"/>
+      <c r="K340" s="57" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" ht="28.8">
+      <c r="A341" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I338" s="11" t="s">
+      <c r="I341" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J338" s="30" t="s">
+      <c r="J341" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K338" t="s">
-        <v>1791</v>
-      </c>
-    </row>
-    <row r="339" spans="1:11">
-      <c r="A339" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B339" s="13"/>
-      <c r="C339" s="49"/>
-      <c r="D339" s="11" t="s">
+      <c r="K341" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11">
+      <c r="A342" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B342" s="13"/>
+      <c r="C342" s="49"/>
+      <c r="D342" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I339" s="11" t="s">
-        <v>1718</v>
-      </c>
-      <c r="J339" s="30"/>
-      <c r="K339" s="57" t="s">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" ht="28.8">
-      <c r="A340" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C340" s="1"/>
-      <c r="D340" s="1" t="s">
+      <c r="I342" s="11" t="s">
+        <v>1728</v>
+      </c>
+      <c r="J342" s="30"/>
+      <c r="K342" s="57" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" ht="28.8">
+      <c r="A343" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I340" s="11" t="s">
+      <c r="I343" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J340" s="30" t="s">
+      <c r="J343" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K340" t="s">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11">
-      <c r="A341" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B341" s="13"/>
-      <c r="C341" s="49"/>
-      <c r="D341" s="11" t="s">
+      <c r="K343" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11">
+      <c r="A344" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B344" s="13"/>
+      <c r="C344" s="49"/>
+      <c r="D344" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I341" s="11" t="s">
-        <v>1731</v>
-      </c>
-      <c r="J341" s="30"/>
-      <c r="K341" s="57" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="342" spans="1:11" ht="28.8">
-      <c r="A342" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C342" s="1"/>
-      <c r="D342" s="1" t="s">
+      <c r="I344" s="11" t="s">
+        <v>1722</v>
+      </c>
+      <c r="J344" s="30"/>
+      <c r="K344" s="57" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" ht="28.8">
+      <c r="A345" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I342" s="11" t="s">
+      <c r="I345" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J342" s="30" t="s">
+      <c r="J345" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K342" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11">
-      <c r="A343" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B343" s="13"/>
-      <c r="C343" s="49"/>
-      <c r="D343" s="11" t="s">
+      <c r="K345" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11">
+      <c r="A346" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B346" s="13"/>
+      <c r="C346" s="49"/>
+      <c r="D346" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I343" s="11" t="s">
-        <v>1732</v>
-      </c>
-      <c r="J343" s="30"/>
-      <c r="K343" s="57" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="344" spans="1:11" ht="28.8">
-      <c r="A344" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C344" s="1"/>
-      <c r="D344" s="1" t="s">
+      <c r="I346" s="11" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J346" s="30"/>
+      <c r="K346" s="57" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" ht="28.8">
+      <c r="A347" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I344" s="11" t="s">
+      <c r="I347" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J344" s="30" t="s">
+      <c r="J347" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K344" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="345" spans="1:11">
-      <c r="A345" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B345" s="13"/>
-      <c r="C345" s="49"/>
-      <c r="D345" s="11" t="s">
+      <c r="K347" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11">
+      <c r="A348" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B348" s="13"/>
+      <c r="C348" s="49"/>
+      <c r="D348" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I345" s="11" t="s">
-        <v>1726</v>
-      </c>
-      <c r="J345" s="30"/>
-      <c r="K345" s="57" t="s">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="346" spans="1:11" ht="28.8">
-      <c r="A346" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C346" s="1"/>
-      <c r="D346" s="1" t="s">
+      <c r="I348" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J348" s="30"/>
+      <c r="K348" s="57" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" ht="28.8">
+      <c r="A349" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I346" s="11" t="s">
+      <c r="I349" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J346" s="30" t="s">
+      <c r="J349" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K346" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="347" spans="1:11">
-      <c r="A347" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="B347" s="13"/>
-      <c r="C347" s="49"/>
-      <c r="D347" s="11" t="s">
+      <c r="K349" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11">
+      <c r="A350" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B350" s="13"/>
+      <c r="C350" s="49"/>
+      <c r="D350" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I347" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J347" s="30"/>
-      <c r="K347" s="57" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" ht="28.8">
-      <c r="A348" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C348" s="1"/>
-      <c r="D348" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I348" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J348" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K348" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11">
-      <c r="A349" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B349" s="13"/>
-      <c r="C349" s="49"/>
-      <c r="D349" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I349" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J349" s="30"/>
-      <c r="K349" s="57" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11" ht="28.8">
-      <c r="A350" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="C350" s="1"/>
-      <c r="D350" s="1" t="s">
-        <v>803</v>
-      </c>
       <c r="I350" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J350" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K350" t="s">
-        <v>1803</v>
+        <v>1730</v>
+      </c>
+      <c r="J350" s="30"/>
+      <c r="K350" s="57" t="s">
+        <v>1779</v>
       </c>
     </row>
     <row r="351" spans="1:11" ht="28.8">
       <c r="A351" s="1" t="s">
-        <v>701</v>
+        <v>464</v>
       </c>
       <c r="C351" s="1"/>
       <c r="D351" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I351" s="11" t="s">
         <v>856</v>
@@ -19628,12 +19745,12 @@
         <v>857</v>
       </c>
       <c r="K351" t="s">
-        <v>1804</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="1" t="s">
-        <v>658</v>
+        <v>454</v>
       </c>
       <c r="B352" s="13"/>
       <c r="C352" s="49"/>
@@ -19641,16 +19758,16 @@
         <v>722</v>
       </c>
       <c r="I352" s="11" t="s">
-        <v>1733</v>
+        <v>1720</v>
       </c>
       <c r="J352" s="30"/>
       <c r="K352" s="57" t="s">
-        <v>1805</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="353" spans="1:11" ht="28.8">
       <c r="A353" s="1" t="s">
-        <v>658</v>
+        <v>454</v>
       </c>
       <c r="C353" s="1"/>
       <c r="D353" s="1" t="s">
@@ -19663,12 +19780,12 @@
         <v>857</v>
       </c>
       <c r="K353" t="s">
-        <v>1806</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="354" spans="1:11">
       <c r="A354" s="1" t="s">
-        <v>629</v>
+        <v>451</v>
       </c>
       <c r="B354" s="13"/>
       <c r="C354" s="49"/>
@@ -19676,16 +19793,16 @@
         <v>722</v>
       </c>
       <c r="I354" s="11" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="J354" s="30"/>
       <c r="K354" s="57" t="s">
-        <v>1807</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="355" spans="1:11" ht="28.8">
       <c r="A355" s="1" t="s">
-        <v>629</v>
+        <v>451</v>
       </c>
       <c r="C355" s="1"/>
       <c r="D355" s="1" t="s">
@@ -19698,12 +19815,12 @@
         <v>857</v>
       </c>
       <c r="K355" t="s">
-        <v>1808</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="356" spans="1:11">
       <c r="A356" s="1" t="s">
-        <v>636</v>
+        <v>422</v>
       </c>
       <c r="B356" s="13"/>
       <c r="C356" s="49"/>
@@ -19711,16 +19828,16 @@
         <v>722</v>
       </c>
       <c r="I356" s="11" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="J356" s="30"/>
       <c r="K356" s="57" t="s">
-        <v>1809</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="357" spans="1:11" ht="28.8">
       <c r="A357" s="1" t="s">
-        <v>636</v>
+        <v>422</v>
       </c>
       <c r="C357" s="1"/>
       <c r="D357" s="1" t="s">
@@ -19733,12 +19850,12 @@
         <v>857</v>
       </c>
       <c r="K357" t="s">
-        <v>1810</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="358" spans="1:11">
       <c r="A358" s="1" t="s">
-        <v>637</v>
+        <v>689</v>
       </c>
       <c r="B358" s="13"/>
       <c r="C358" s="49"/>
@@ -19746,16 +19863,16 @@
         <v>722</v>
       </c>
       <c r="I358" s="11" t="s">
-        <v>1735</v>
+        <v>1722</v>
       </c>
       <c r="J358" s="30"/>
       <c r="K358" s="57" t="s">
-        <v>1811</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="359" spans="1:11" ht="28.8">
       <c r="A359" s="1" t="s">
-        <v>637</v>
+        <v>689</v>
       </c>
       <c r="C359" s="1"/>
       <c r="D359" s="1" t="s">
@@ -19768,12 +19885,12 @@
         <v>857</v>
       </c>
       <c r="K359" t="s">
-        <v>1812</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="360" spans="1:11">
       <c r="A360" s="1" t="s">
-        <v>638</v>
+        <v>407</v>
       </c>
       <c r="B360" s="13"/>
       <c r="C360" s="49"/>
@@ -19781,16 +19898,16 @@
         <v>722</v>
       </c>
       <c r="I360" s="11" t="s">
-        <v>1735</v>
+        <v>1717</v>
       </c>
       <c r="J360" s="30"/>
       <c r="K360" s="57" t="s">
-        <v>1813</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="361" spans="1:11" ht="28.8">
       <c r="A361" s="1" t="s">
-        <v>638</v>
+        <v>407</v>
       </c>
       <c r="C361" s="1"/>
       <c r="D361" s="1" t="s">
@@ -19803,12 +19920,12 @@
         <v>857</v>
       </c>
       <c r="K361" t="s">
-        <v>1814</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="362" spans="1:11">
       <c r="A362" s="1" t="s">
-        <v>645</v>
+        <v>409</v>
       </c>
       <c r="B362" s="13"/>
       <c r="C362" s="49"/>
@@ -19816,16 +19933,16 @@
         <v>722</v>
       </c>
       <c r="I362" s="11" t="s">
-        <v>1736</v>
+        <v>1717</v>
       </c>
       <c r="J362" s="30"/>
       <c r="K362" s="57" t="s">
-        <v>1815</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="363" spans="1:11" ht="28.8">
       <c r="A363" s="1" t="s">
-        <v>645</v>
+        <v>409</v>
       </c>
       <c r="C363" s="1"/>
       <c r="D363" s="1" t="s">
@@ -19838,12 +19955,12 @@
         <v>857</v>
       </c>
       <c r="K363" t="s">
-        <v>1816</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="364" spans="1:11">
       <c r="A364" s="1" t="s">
-        <v>641</v>
+        <v>466</v>
       </c>
       <c r="B364" s="13"/>
       <c r="C364" s="49"/>
@@ -19851,16 +19968,16 @@
         <v>722</v>
       </c>
       <c r="I364" s="11" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
       <c r="J364" s="30"/>
       <c r="K364" s="57" t="s">
-        <v>1817</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="365" spans="1:11" ht="28.8">
       <c r="A365" s="1" t="s">
-        <v>641</v>
+        <v>466</v>
       </c>
       <c r="C365" s="1"/>
       <c r="D365" s="1" t="s">
@@ -19873,139 +19990,138 @@
         <v>857</v>
       </c>
       <c r="K365" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="366" spans="1:11" ht="28.8">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11">
       <c r="A366" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="C366" s="1"/>
-      <c r="D366" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B366" s="13"/>
+      <c r="C366" s="49"/>
+      <c r="D366" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I366" s="11" t="s">
+        <v>1731</v>
+      </c>
+      <c r="J366" s="30"/>
+      <c r="K366" s="57" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" ht="28.8">
+      <c r="A367" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I367" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J366" s="30" t="s">
+      <c r="J367" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K366" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="367" spans="1:11">
-      <c r="A367" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="B367" s="13"/>
-      <c r="C367" s="49"/>
-      <c r="D367" s="11" t="s">
+      <c r="K367" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11">
+      <c r="A368" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B368" s="13"/>
+      <c r="C368" s="49"/>
+      <c r="D368" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I367" s="11" t="s">
-        <v>1738</v>
-      </c>
-      <c r="J367" s="30"/>
-      <c r="K367" s="57" t="s">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="368" spans="1:11" ht="28.8">
-      <c r="A368" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C368" s="1"/>
-      <c r="D368" s="1" t="s">
+      <c r="I368" s="11" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J368" s="30"/>
+      <c r="K368" s="57" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" ht="28.8">
+      <c r="A369" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I368" s="11" t="s">
+      <c r="I369" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J368" s="30" t="s">
+      <c r="J369" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K368" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="369" spans="1:11">
-      <c r="A369" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="B369" s="13"/>
-      <c r="C369" s="49"/>
-      <c r="D369" s="11" t="s">
+      <c r="K369" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11">
+      <c r="A370" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B370" s="13"/>
+      <c r="C370" s="49"/>
+      <c r="D370" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I369" s="11" t="s">
-        <v>1739</v>
-      </c>
-      <c r="J369" s="30"/>
-      <c r="K369" s="57" t="s">
-        <v>1822</v>
-      </c>
-    </row>
-    <row r="370" spans="1:11" ht="28.8">
-      <c r="A370" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C370" s="1"/>
-      <c r="D370" s="1" t="s">
+      <c r="I370" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J370" s="30"/>
+      <c r="K370" s="57" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" ht="28.8">
+      <c r="A371" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I370" s="11" t="s">
+      <c r="I371" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J370" s="30" t="s">
+      <c r="J371" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K370" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="371" spans="1:11">
-      <c r="A371" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B371" s="13"/>
-      <c r="C371" s="49"/>
-      <c r="D371" s="11" t="s">
+      <c r="K371" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11">
+      <c r="A372" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B372" s="13"/>
+      <c r="C372" s="49"/>
+      <c r="D372" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I371" s="11" t="s">
-        <v>1740</v>
-      </c>
-      <c r="J371" s="30"/>
-      <c r="K371" s="57" t="s">
-        <v>1824</v>
-      </c>
-    </row>
-    <row r="372" spans="1:11" ht="28.8">
-      <c r="A372" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C372" s="1"/>
-      <c r="D372" s="1" t="s">
-        <v>803</v>
-      </c>
       <c r="I372" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J372" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K372" t="s">
-        <v>1825</v>
+        <v>1723</v>
+      </c>
+      <c r="J372" s="30"/>
+      <c r="K372" s="57" t="s">
+        <v>1801</v>
       </c>
     </row>
     <row r="373" spans="1:11" ht="28.8">
       <c r="A373" s="1" t="s">
-        <v>703</v>
+        <v>597</v>
       </c>
       <c r="C373" s="1"/>
       <c r="D373" s="1" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="I373" s="11" t="s">
         <v>856</v>
@@ -20014,278 +20130,279 @@
         <v>857</v>
       </c>
       <c r="K373" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="374" spans="1:11">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" ht="28.8">
       <c r="A374" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="B374" s="13"/>
-      <c r="C374" s="49"/>
-      <c r="D374" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I374" s="11" t="s">
-        <v>1741</v>
-      </c>
-      <c r="J374" s="30"/>
-      <c r="K374" s="57" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="375" spans="1:11" ht="28.8">
+        <v>856</v>
+      </c>
+      <c r="J374" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K374" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11">
       <c r="A375" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C375" s="1"/>
-      <c r="D375" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B375" s="13"/>
+      <c r="C375" s="49"/>
+      <c r="D375" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I375" s="11" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J375" s="30"/>
+      <c r="K375" s="57" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" ht="28.8">
+      <c r="A376" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I375" s="11" t="s">
+      <c r="I376" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J375" s="30" t="s">
+      <c r="J376" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K375" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="376" spans="1:11">
-      <c r="A376" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B376" s="13"/>
-      <c r="C376" s="49"/>
-      <c r="D376" s="11" t="s">
+      <c r="K376" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11">
+      <c r="A377" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B377" s="13"/>
+      <c r="C377" s="49"/>
+      <c r="D377" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I376" s="11" t="s">
+      <c r="I377" s="11" t="s">
         <v>1733</v>
       </c>
-      <c r="J376" s="30"/>
-      <c r="K376" s="57" t="s">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="377" spans="1:11" ht="28.8">
-      <c r="A377" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C377" s="1"/>
-      <c r="D377" s="1" t="s">
+      <c r="J377" s="30"/>
+      <c r="K377" s="57" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" ht="28.8">
+      <c r="A378" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I377" s="11" t="s">
+      <c r="I378" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J377" s="30" t="s">
+      <c r="J378" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K377" t="s">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="378" spans="1:11">
-      <c r="A378" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="B378" s="13"/>
-      <c r="C378" s="49"/>
-      <c r="D378" s="11" t="s">
+      <c r="K378" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11">
+      <c r="A379" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B379" s="13"/>
+      <c r="C379" s="49"/>
+      <c r="D379" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I378" s="11" t="s">
-        <v>1719</v>
-      </c>
-      <c r="J378" s="30"/>
-      <c r="K378" s="57" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="379" spans="1:11" ht="28.8">
-      <c r="A379" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="C379" s="1"/>
-      <c r="D379" s="1" t="s">
+      <c r="I379" s="11" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J379" s="30"/>
+      <c r="K379" s="57" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" ht="28.8">
+      <c r="A380" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I379" s="11" t="s">
+      <c r="I380" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J379" s="30" t="s">
+      <c r="J380" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K379" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="380" spans="1:11">
-      <c r="A380" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="B380" s="13"/>
-      <c r="C380" s="49"/>
-      <c r="D380" s="11" t="s">
+      <c r="K380" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11">
+      <c r="A381" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B381" s="13"/>
+      <c r="C381" s="49"/>
+      <c r="D381" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I380" s="11" t="s">
-        <v>1719</v>
-      </c>
-      <c r="J380" s="30"/>
-      <c r="K380" s="57" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="381" spans="1:11" ht="28.8">
-      <c r="A381" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C381" s="1"/>
-      <c r="D381" s="1" t="s">
+      <c r="I381" s="11" t="s">
+        <v>1734</v>
+      </c>
+      <c r="J381" s="30"/>
+      <c r="K381" s="57" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" ht="28.8">
+      <c r="A382" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I381" s="11" t="s">
+      <c r="I382" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J381" s="30" t="s">
+      <c r="J382" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K381" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="382" spans="1:11">
-      <c r="A382" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="B382" s="13"/>
-      <c r="C382" s="49"/>
-      <c r="D382" s="11" t="s">
+      <c r="K382" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11">
+      <c r="A383" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B383" s="13"/>
+      <c r="C383" s="49"/>
+      <c r="D383" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I382" s="11" t="s">
-        <v>1742</v>
-      </c>
-      <c r="J382" s="30"/>
-      <c r="K382" s="57" t="s">
-        <v>1835</v>
-      </c>
-    </row>
-    <row r="383" spans="1:11" ht="28.8">
-      <c r="A383" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="C383" s="1"/>
-      <c r="D383" s="1" t="s">
+      <c r="I383" s="11" t="s">
+        <v>1734</v>
+      </c>
+      <c r="J383" s="30"/>
+      <c r="K383" s="57" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" ht="28.8">
+      <c r="A384" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I383" s="11" t="s">
+      <c r="I384" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J383" s="30" t="s">
+      <c r="J384" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K383" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="384" spans="1:11">
-      <c r="A384" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B384" s="13"/>
-      <c r="C384" s="49"/>
-      <c r="D384" s="11" t="s">
+      <c r="K384" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11">
+      <c r="A385" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B385" s="13"/>
+      <c r="C385" s="49"/>
+      <c r="D385" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I384" s="11" t="s">
-        <v>1721</v>
-      </c>
-      <c r="J384" s="30"/>
-      <c r="K384" s="57" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="385" spans="1:11" ht="28.8">
-      <c r="A385" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="C385" s="1"/>
-      <c r="D385" s="1" t="s">
+      <c r="I385" s="11" t="s">
+        <v>1735</v>
+      </c>
+      <c r="J385" s="30"/>
+      <c r="K385" s="57" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" ht="28.8">
+      <c r="A386" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C386" s="1"/>
+      <c r="D386" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I385" s="11" t="s">
+      <c r="I386" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J385" s="30" t="s">
+      <c r="J386" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K385" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="386" spans="1:11">
-      <c r="A386" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B386" s="13"/>
-      <c r="C386" s="49"/>
-      <c r="D386" s="11" t="s">
+      <c r="K386" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11">
+      <c r="A387" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B387" s="13"/>
+      <c r="C387" s="49"/>
+      <c r="D387" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I386" s="11" t="s">
-        <v>1743</v>
-      </c>
-      <c r="J386" s="30"/>
-      <c r="K386" s="57" t="s">
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="387" spans="1:11" ht="28.8">
-      <c r="A387" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C387" s="1"/>
-      <c r="D387" s="1" t="s">
+      <c r="I387" s="11" t="s">
+        <v>1736</v>
+      </c>
+      <c r="J387" s="30"/>
+      <c r="K387" s="57" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" ht="28.8">
+      <c r="A388" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C388" s="1"/>
+      <c r="D388" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I387" s="11" t="s">
+      <c r="I388" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J387" s="30" t="s">
+      <c r="J388" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K387" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="388" spans="1:11">
-      <c r="A388" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B388" s="13"/>
-      <c r="C388" s="49"/>
-      <c r="D388" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I388" s="11" t="s">
-        <v>1721</v>
-      </c>
-      <c r="J388" s="30"/>
-      <c r="K388" s="57" t="s">
-        <v>1841</v>
+      <c r="K388" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="389" spans="1:11" ht="28.8">
       <c r="A389" s="1" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="C389" s="1"/>
       <c r="D389" s="1" t="s">
-        <v>803</v>
+        <v>722</v>
       </c>
       <c r="I389" s="11" t="s">
         <v>856</v>
@@ -20294,12 +20411,12 @@
         <v>857</v>
       </c>
       <c r="K389" t="s">
-        <v>1842</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="390" spans="1:11">
       <c r="A390" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B390" s="13"/>
       <c r="C390" s="49"/>
@@ -20307,16 +20424,16 @@
         <v>722</v>
       </c>
       <c r="I390" s="11" t="s">
-        <v>1721</v>
+        <v>1737</v>
       </c>
       <c r="J390" s="30"/>
       <c r="K390" s="57" t="s">
-        <v>1843</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="391" spans="1:11" ht="28.8">
       <c r="A391" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C391" s="1"/>
       <c r="D391" s="1" t="s">
@@ -20329,12 +20446,12 @@
         <v>857</v>
       </c>
       <c r="K391" t="s">
-        <v>1844</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="392" spans="1:11">
       <c r="A392" s="1" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="B392" s="13"/>
       <c r="C392" s="49"/>
@@ -20342,16 +20459,16 @@
         <v>722</v>
       </c>
       <c r="I392" s="11" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
       <c r="J392" s="30"/>
       <c r="K392" s="57" t="s">
-        <v>1845</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="393" spans="1:11" ht="28.8">
       <c r="A393" s="1" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="C393" s="1"/>
       <c r="D393" s="1" t="s">
@@ -20364,12 +20481,12 @@
         <v>857</v>
       </c>
       <c r="K393" t="s">
-        <v>1846</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="394" spans="1:11">
       <c r="A394" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B394" s="13"/>
       <c r="C394" s="49"/>
@@ -20377,16 +20494,16 @@
         <v>722</v>
       </c>
       <c r="I394" s="11" t="s">
-        <v>1724</v>
+        <v>1739</v>
       </c>
       <c r="J394" s="30"/>
       <c r="K394" s="57" t="s">
-        <v>1847</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="395" spans="1:11" ht="28.8">
       <c r="A395" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C395" s="1"/>
       <c r="D395" s="1" t="s">
@@ -20399,257 +20516,257 @@
         <v>857</v>
       </c>
       <c r="K395" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="396" spans="1:11">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" ht="28.8">
       <c r="A396" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="B396" s="13"/>
-      <c r="C396" s="49"/>
-      <c r="D396" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="C396" s="1"/>
+      <c r="D396" s="1" t="s">
         <v>722</v>
       </c>
       <c r="I396" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J396" s="30"/>
-      <c r="K396" s="57" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="397" spans="1:11" ht="28.8">
+        <v>856</v>
+      </c>
+      <c r="J396" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K396" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11">
       <c r="A397" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C397" s="1"/>
-      <c r="D397" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B397" s="13"/>
+      <c r="C397" s="49"/>
+      <c r="D397" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I397" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="J397" s="30"/>
+      <c r="K397" s="57" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" ht="28.8">
+      <c r="A398" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C398" s="1"/>
+      <c r="D398" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I397" s="11" t="s">
+      <c r="I398" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J397" s="30" t="s">
+      <c r="J398" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K397" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="398" spans="1:11">
-      <c r="A398" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B398" s="13"/>
-      <c r="C398" s="49"/>
-      <c r="D398" s="11" t="s">
+      <c r="K398" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11">
+      <c r="A399" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B399" s="13"/>
+      <c r="C399" s="49"/>
+      <c r="D399" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I398" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="J398" s="30"/>
-      <c r="K398" s="57" t="s">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="399" spans="1:11" ht="28.8">
-      <c r="A399" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C399" s="1"/>
-      <c r="D399" s="1" t="s">
+      <c r="I399" s="11" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J399" s="30"/>
+      <c r="K399" s="57" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" ht="28.8">
+      <c r="A400" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C400" s="1"/>
+      <c r="D400" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I399" s="11" t="s">
+      <c r="I400" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J399" s="30" t="s">
+      <c r="J400" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K399" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="400" spans="1:11">
-      <c r="A400" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B400" s="13"/>
-      <c r="C400" s="49"/>
-      <c r="D400" s="11" t="s">
+      <c r="K400" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11">
+      <c r="A401" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B401" s="13"/>
+      <c r="C401" s="49"/>
+      <c r="D401" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="I400" s="11" t="s">
+      <c r="I401" s="11" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J401" s="30"/>
+      <c r="K401" s="57" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" ht="28.8">
+      <c r="A402" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C402" s="1"/>
+      <c r="D402" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I402" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J402" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K402" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11">
+      <c r="A403" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B403" s="13"/>
+      <c r="C403" s="49"/>
+      <c r="D403" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I403" s="11" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J403" s="30"/>
+      <c r="K403" s="57" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" ht="28.8">
+      <c r="A404" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C404" s="1"/>
+      <c r="D404" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I404" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J404" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K404" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11">
+      <c r="A405" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B405" s="13"/>
+      <c r="C405" s="49"/>
+      <c r="D405" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I405" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J405" s="30"/>
+      <c r="K405" s="57" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" ht="28.8">
+      <c r="A406" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I406" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J406" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K406" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11">
+      <c r="A407" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B407" s="13"/>
+      <c r="C407" s="49"/>
+      <c r="D407" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I407" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J407" s="30"/>
+      <c r="K407" s="57" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" ht="28.8">
+      <c r="A408" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C408" s="1"/>
+      <c r="D408" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I408" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J408" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K408" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11">
+      <c r="A409" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B409" s="13"/>
+      <c r="C409" s="49"/>
+      <c r="D409" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I409" s="11" t="s">
         <v>1742</v>
       </c>
-      <c r="J400" s="30"/>
-      <c r="K400" s="57" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="401" spans="1:11" ht="28.8">
-      <c r="A401" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C401" s="1"/>
-      <c r="D401" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I401" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J401" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K401" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="402" spans="1:11">
-      <c r="A402" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="B402" s="13"/>
-      <c r="C402" s="49"/>
-      <c r="D402" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I402" s="11" t="s">
-        <v>1742</v>
-      </c>
-      <c r="J402" s="30"/>
-      <c r="K402" s="57" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="403" spans="1:11" ht="28.8">
-      <c r="A403" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C403" s="1"/>
-      <c r="D403" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I403" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J403" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K403" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="404" spans="1:11">
-      <c r="A404" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B404" s="13"/>
-      <c r="C404" s="49"/>
-      <c r="D404" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I404" s="11" t="s">
-        <v>1745</v>
-      </c>
-      <c r="J404" s="30"/>
-      <c r="K404" s="57" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="405" spans="1:11" ht="28.8">
-      <c r="A405" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C405" s="1"/>
-      <c r="D405" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I405" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J405" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K405" t="s">
-        <v>1858</v>
-      </c>
-    </row>
-    <row r="406" spans="1:11">
-      <c r="A406" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="B406" s="13"/>
-      <c r="C406" s="49"/>
-      <c r="D406" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I406" s="11" t="s">
-        <v>1725</v>
-      </c>
-      <c r="J406" s="30"/>
-      <c r="K406" s="57" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="407" spans="1:11" ht="28.8">
-      <c r="A407" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="C407" s="1"/>
-      <c r="D407" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I407" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J407" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K407" t="s">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="408" spans="1:11">
-      <c r="A408" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="B408" s="13"/>
-      <c r="C408" s="49"/>
-      <c r="D408" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I408" s="11" t="s">
-        <v>1742</v>
-      </c>
-      <c r="J408" s="30"/>
-      <c r="K408" s="57" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="409" spans="1:11" ht="28.8">
-      <c r="A409" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="C409" s="1"/>
-      <c r="D409" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I409" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="J409" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="K409" t="s">
-        <v>1862</v>
+      <c r="J409" s="30"/>
+      <c r="K409" s="57" t="s">
+        <v>1838</v>
       </c>
     </row>
     <row r="410" spans="1:11" ht="28.8">
       <c r="A410" s="1" t="s">
-        <v>704</v>
+        <v>679</v>
       </c>
       <c r="C410" s="1"/>
       <c r="D410" s="1" t="s">
@@ -20662,337 +20779,671 @@
         <v>857</v>
       </c>
       <c r="K410" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="411" spans="1:11" ht="28.8">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11">
       <c r="A411" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C411" s="1"/>
-      <c r="D411" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B411" s="13"/>
+      <c r="C411" s="49"/>
+      <c r="D411" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I411" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J411" s="30"/>
+      <c r="K411" s="57" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" ht="28.8">
+      <c r="A412" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C412" s="1"/>
+      <c r="D412" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I411" s="11" t="s">
+      <c r="I412" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J411" s="30" t="s">
+      <c r="J412" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K411" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="412" spans="1:11">
-      <c r="A412" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B412" s="13"/>
-      <c r="C412" s="49"/>
-      <c r="D412" s="11" t="s">
+      <c r="K412" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11">
+      <c r="A413" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B413" s="13"/>
+      <c r="C413" s="49"/>
+      <c r="D413" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I413" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="J413" s="30"/>
+      <c r="K413" s="57" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" ht="28.8">
+      <c r="A414" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C414" s="1"/>
+      <c r="D414" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="I412" s="11" t="s">
-        <v>1742</v>
-      </c>
-      <c r="J412" s="30"/>
-      <c r="K412" s="57" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="413" spans="1:11" ht="28.8">
-      <c r="A413" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="C413" s="1"/>
-      <c r="D413" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="I413" s="11" t="s">
+      <c r="I414" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="J413" s="30" t="s">
+      <c r="J414" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="K413" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="414" spans="1:11">
-      <c r="A414" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C414" s="1"/>
-      <c r="D414" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="I414" s="11" t="s">
-        <v>1875</v>
-      </c>
-      <c r="J414" s="30" t="s">
-        <v>1887</v>
-      </c>
       <c r="K414" t="s">
-        <v>1878</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="415" spans="1:11">
-      <c r="A415" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="C415" s="1"/>
+      <c r="A415" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B415" s="13"/>
+      <c r="C415" s="49"/>
       <c r="D415" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I415" s="11" t="s">
-        <v>1874</v>
-      </c>
-      <c r="J415" s="30" t="s">
-        <v>1887</v>
-      </c>
-      <c r="K415" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="416" spans="1:11">
-      <c r="A416" s="13" t="s">
-        <v>408</v>
+        <v>1743</v>
+      </c>
+      <c r="J415" s="30"/>
+      <c r="K415" s="57" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" ht="28.8">
+      <c r="A416" s="1" t="s">
+        <v>661</v>
       </c>
       <c r="C416" s="1"/>
-      <c r="D416" s="11" t="s">
-        <v>722</v>
+      <c r="D416" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="I416" s="11" t="s">
-        <v>1876</v>
+        <v>856</v>
       </c>
       <c r="J416" s="30" t="s">
-        <v>1887</v>
+        <v>857</v>
       </c>
       <c r="K416" t="s">
-        <v>1880</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="417" spans="1:11">
-      <c r="A417" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="C417" s="1"/>
+      <c r="A417" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B417" s="13"/>
+      <c r="C417" s="49"/>
       <c r="D417" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I417" s="11" t="s">
-        <v>1874</v>
-      </c>
-      <c r="J417" s="30" t="s">
-        <v>1887</v>
-      </c>
-      <c r="K417" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="418" spans="1:11">
-      <c r="A418" s="13" t="s">
-        <v>457</v>
+        <v>1723</v>
+      </c>
+      <c r="J417" s="30"/>
+      <c r="K417" s="57" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" ht="28.8">
+      <c r="A418" s="1" t="s">
+        <v>655</v>
       </c>
       <c r="C418" s="1"/>
-      <c r="D418" s="11" t="s">
-        <v>722</v>
+      <c r="D418" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="I418" s="11" t="s">
-        <v>1874</v>
+        <v>856</v>
       </c>
       <c r="J418" s="30" t="s">
-        <v>1887</v>
+        <v>857</v>
       </c>
       <c r="K418" t="s">
-        <v>1882</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="419" spans="1:11">
-      <c r="A419" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="C419" s="1"/>
+      <c r="A419" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B419" s="13"/>
+      <c r="C419" s="49"/>
       <c r="D419" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I419" s="11" t="s">
-        <v>1874</v>
-      </c>
-      <c r="J419" s="30" t="s">
-        <v>1887</v>
-      </c>
-      <c r="K419" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="420" spans="1:11">
-      <c r="A420" s="13" t="s">
-        <v>426</v>
+        <v>1723</v>
+      </c>
+      <c r="J419" s="30"/>
+      <c r="K419" s="57" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" ht="28.8">
+      <c r="A420" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="C420" s="1"/>
-      <c r="D420" s="11" t="s">
-        <v>722</v>
+      <c r="D420" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="I420" s="11" t="s">
-        <v>1874</v>
+        <v>856</v>
       </c>
       <c r="J420" s="30" t="s">
-        <v>1887</v>
+        <v>857</v>
       </c>
       <c r="K420" t="s">
-        <v>1884</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="421" spans="1:11">
-      <c r="A421" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="C421" s="1"/>
+      <c r="A421" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B421" s="13"/>
+      <c r="C421" s="49"/>
       <c r="D421" s="11" t="s">
         <v>722</v>
       </c>
       <c r="I421" s="11" t="s">
-        <v>1877</v>
-      </c>
-      <c r="J421" s="30" t="s">
-        <v>1887</v>
-      </c>
-      <c r="K421" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="422" spans="1:11">
-      <c r="A422" s="13" t="s">
-        <v>624</v>
+        <v>1723</v>
+      </c>
+      <c r="J421" s="30"/>
+      <c r="K421" s="57" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" ht="28.8">
+      <c r="A422" s="1" t="s">
+        <v>662</v>
       </c>
       <c r="C422" s="1"/>
-      <c r="D422" s="11" t="s">
-        <v>722</v>
+      <c r="D422" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="I422" s="11" t="s">
-        <v>1874</v>
+        <v>856</v>
       </c>
       <c r="J422" s="30" t="s">
-        <v>1887</v>
+        <v>857</v>
       </c>
       <c r="K422" t="s">
-        <v>1886</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="423" spans="1:11">
       <c r="A423" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B423" s="13"/>
+      <c r="C423" s="49"/>
+      <c r="D423" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I423" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J423" s="30"/>
+      <c r="K423" s="57" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" ht="28.8">
+      <c r="A424" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C424" s="1"/>
+      <c r="D424" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I424" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J424" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K424" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11">
+      <c r="A425" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B425" s="13"/>
+      <c r="C425" s="49"/>
+      <c r="D425" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I425" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J425" s="30"/>
+      <c r="K425" s="57" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" ht="28.8">
+      <c r="A426" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C426" s="1"/>
+      <c r="D426" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I426" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J426" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K426" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11">
+      <c r="A427" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B427" s="13"/>
+      <c r="C427" s="49"/>
+      <c r="D427" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I427" s="11" t="s">
+        <v>1744</v>
+      </c>
+      <c r="J427" s="30"/>
+      <c r="K427" s="57" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" ht="28.8">
+      <c r="A428" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C428" s="1"/>
+      <c r="D428" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I428" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J428" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K428" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11">
+      <c r="A429" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B429" s="13"/>
+      <c r="C429" s="49"/>
+      <c r="D429" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I429" s="11" t="s">
+        <v>1724</v>
+      </c>
+      <c r="J429" s="30"/>
+      <c r="K429" s="57" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" ht="28.8">
+      <c r="A430" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C430" s="1"/>
+      <c r="D430" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I430" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J430" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K430" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11">
+      <c r="A431" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B431" s="13"/>
+      <c r="C431" s="49"/>
+      <c r="D431" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I431" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J431" s="30"/>
+      <c r="K431" s="57" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" ht="28.8">
+      <c r="A432" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C432" s="1"/>
+      <c r="D432" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I432" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J432" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K432" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" ht="28.8">
+      <c r="A433" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I433" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J433" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K433" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" ht="28.8">
+      <c r="A434" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I434" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J434" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K434" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11">
+      <c r="A435" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B435" s="13"/>
+      <c r="C435" s="49"/>
+      <c r="D435" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="I435" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J435" s="30"/>
+      <c r="K435" s="57" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" ht="28.8">
+      <c r="A436" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I436" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="J436" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="K436" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11">
+      <c r="A437" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C437" s="1"/>
+      <c r="D437" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I437" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="J437" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K437" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11">
+      <c r="A438" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="C438" s="1"/>
+      <c r="D438" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I438" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J438" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K438" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11">
+      <c r="A439" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C439" s="1"/>
+      <c r="D439" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I439" s="11" t="s">
+        <v>1875</v>
+      </c>
+      <c r="J439" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K439" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11">
+      <c r="A440" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="C440" s="1"/>
+      <c r="D440" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I440" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J440" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K440" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11">
+      <c r="A441" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="C441" s="1"/>
+      <c r="D441" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I441" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J441" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K441" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11">
+      <c r="A442" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C442" s="1"/>
+      <c r="D442" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I442" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J442" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K442" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11">
+      <c r="A443" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="C443" s="1"/>
+      <c r="D443" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I443" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J443" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K443" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11">
+      <c r="A444" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C444" s="1"/>
+      <c r="D444" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I444" s="11" t="s">
+        <v>1876</v>
+      </c>
+      <c r="J444" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K444" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11">
+      <c r="A445" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="C445" s="1"/>
+      <c r="D445" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="I445" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J445" s="30" t="s">
+        <v>1886</v>
+      </c>
+      <c r="K445" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11">
+      <c r="A446" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D423" s="1" t="s">
+      <c r="D446" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="J423" s="30" t="s">
+      <c r="J446" s="30" t="s">
         <v>718</v>
       </c>
-      <c r="K423" t="s">
+      <c r="K446" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
-      <c r="A424" s="1" t="s">
+    <row r="447" spans="1:11">
+      <c r="A447" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D424" s="1" t="s">
+      <c r="D447" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="J424" s="30" t="s">
+      <c r="J447" s="30" t="s">
         <v>718</v>
       </c>
-      <c r="K424" t="s">
+      <c r="K447" t="s">
         <v>1501</v>
       </c>
     </row>
-    <row r="1029" spans="6:8">
-      <c r="F1029" s="30"/>
-      <c r="H1029" s="30"/>
-    </row>
-    <row r="1030" spans="6:8">
-      <c r="F1030" s="30"/>
-    </row>
-    <row r="1031" spans="6:8">
-      <c r="F1031" s="30"/>
-      <c r="H1031" s="30"/>
-    </row>
-    <row r="1100" spans="8:8">
-      <c r="H1100" s="52"/>
-    </row>
-    <row r="1754" spans="6:8">
-      <c r="H1754" s="30"/>
-    </row>
-    <row r="1755" spans="6:8">
-      <c r="F1755" s="30"/>
-      <c r="H1755" s="30"/>
-    </row>
-    <row r="1756" spans="6:8">
-      <c r="F1756" s="30"/>
-      <c r="H1756" s="30"/>
-    </row>
-    <row r="1757" spans="6:8">
-      <c r="F1757" s="30"/>
-      <c r="H1757" s="30"/>
-    </row>
-    <row r="1758" spans="6:8">
-      <c r="F1758" s="30"/>
-      <c r="H1758" s="30"/>
-    </row>
-    <row r="1759" spans="6:8">
-      <c r="F1759" s="30"/>
-      <c r="H1759" s="30"/>
-    </row>
-    <row r="1760" spans="6:8">
-      <c r="F1760" s="30"/>
-      <c r="H1760" s="30"/>
-    </row>
-    <row r="1761" spans="6:8">
-      <c r="F1761" s="30"/>
-      <c r="H1761" s="30"/>
-    </row>
-    <row r="1762" spans="6:8">
-      <c r="H1762" s="30"/>
-    </row>
-    <row r="1764" spans="6:8">
-      <c r="H1764" s="30"/>
-    </row>
-    <row r="1766" spans="6:8">
-      <c r="H1766" s="30"/>
-    </row>
-    <row r="1768" spans="6:8">
-      <c r="H1768" s="30"/>
-    </row>
-    <row r="1770" spans="6:8">
-      <c r="H1770" s="30"/>
-    </row>
-    <row r="1771" spans="6:8">
-      <c r="F1771" s="30"/>
-      <c r="H1771" s="30"/>
-    </row>
-    <row r="1772" spans="6:8">
-      <c r="H1772" s="30"/>
-    </row>
-    <row r="1773" spans="6:8">
-      <c r="F1773" s="30"/>
-      <c r="H1773" s="53"/>
-    </row>
-    <row r="1774" spans="6:8">
-      <c r="H1774" s="30"/>
-    </row>
-    <row r="1775" spans="6:8">
-      <c r="F1775" s="54"/>
-      <c r="H1775" s="53"/>
-    </row>
-    <row r="1776" spans="6:8">
-      <c r="F1776" s="30"/>
-      <c r="H1776" s="30"/>
+    <row r="1052" spans="6:8">
+      <c r="F1052" s="30"/>
+      <c r="H1052" s="30"/>
+    </row>
+    <row r="1053" spans="6:8">
+      <c r="F1053" s="30"/>
+    </row>
+    <row r="1054" spans="6:8">
+      <c r="F1054" s="30"/>
+      <c r="H1054" s="30"/>
+    </row>
+    <row r="1123" spans="8:8">
+      <c r="H1123" s="52"/>
     </row>
     <row r="1777" spans="6:8">
-      <c r="F1777" s="30"/>
-      <c r="H1777" s="53"/>
+      <c r="H1777" s="30"/>
     </row>
     <row r="1778" spans="6:8">
       <c r="F1778" s="30"/>
@@ -21000,130 +21451,84 @@
     </row>
     <row r="1779" spans="6:8">
       <c r="F1779" s="30"/>
-      <c r="H1779" s="53"/>
+      <c r="H1779" s="30"/>
     </row>
     <row r="1780" spans="6:8">
       <c r="F1780" s="30"/>
       <c r="H1780" s="30"/>
     </row>
     <row r="1781" spans="6:8">
-      <c r="F1781" s="53"/>
-      <c r="H1781" s="53"/>
+      <c r="F1781" s="30"/>
+      <c r="H1781" s="30"/>
     </row>
     <row r="1782" spans="6:8">
       <c r="F1782" s="30"/>
-      <c r="G1782" s="30"/>
       <c r="H1782" s="30"/>
     </row>
     <row r="1783" spans="6:8">
       <c r="F1783" s="30"/>
-      <c r="G1783" s="30"/>
       <c r="H1783" s="30"/>
     </row>
     <row r="1784" spans="6:8">
       <c r="F1784" s="30"/>
-      <c r="G1784" s="30"/>
       <c r="H1784" s="30"/>
     </row>
     <row r="1785" spans="6:8">
-      <c r="F1785" s="30"/>
-      <c r="G1785" s="30"/>
       <c r="H1785" s="30"/>
     </row>
-    <row r="1786" spans="6:8">
-      <c r="F1786" s="30"/>
-      <c r="G1786" s="30"/>
-      <c r="H1786" s="30"/>
-    </row>
     <row r="1787" spans="6:8">
-      <c r="F1787" s="30"/>
-      <c r="G1787" s="30"/>
       <c r="H1787" s="30"/>
     </row>
-    <row r="1788" spans="6:8">
-      <c r="F1788" s="30"/>
-      <c r="G1788" s="30"/>
-      <c r="H1788" s="30"/>
-    </row>
     <row r="1789" spans="6:8">
-      <c r="F1789" s="30"/>
-      <c r="G1789" s="30"/>
       <c r="H1789" s="30"/>
     </row>
-    <row r="1790" spans="6:8">
-      <c r="F1790" s="30"/>
-      <c r="G1790" s="30"/>
-      <c r="H1790" s="30"/>
-    </row>
     <row r="1791" spans="6:8">
-      <c r="F1791" s="30"/>
-      <c r="G1791" s="30"/>
       <c r="H1791" s="30"/>
     </row>
-    <row r="1792" spans="6:8">
-      <c r="F1792" s="30"/>
-      <c r="G1792" s="30"/>
-      <c r="H1792" s="30"/>
-    </row>
     <row r="1793" spans="6:8">
-      <c r="F1793" s="30"/>
-      <c r="G1793" s="30"/>
       <c r="H1793" s="30"/>
     </row>
     <row r="1794" spans="6:8">
       <c r="F1794" s="30"/>
-      <c r="G1794" s="30"/>
       <c r="H1794" s="30"/>
     </row>
     <row r="1795" spans="6:8">
-      <c r="F1795" s="30"/>
-      <c r="G1795" s="30"/>
       <c r="H1795" s="30"/>
     </row>
     <row r="1796" spans="6:8">
       <c r="F1796" s="30"/>
-      <c r="G1796" s="30"/>
-      <c r="H1796" s="30"/>
+      <c r="H1796" s="53"/>
     </row>
     <row r="1797" spans="6:8">
-      <c r="F1797" s="30"/>
-      <c r="G1797" s="30"/>
       <c r="H1797" s="30"/>
     </row>
     <row r="1798" spans="6:8">
-      <c r="F1798" s="30"/>
-      <c r="G1798" s="30"/>
-      <c r="H1798" s="30"/>
+      <c r="F1798" s="54"/>
+      <c r="H1798" s="53"/>
     </row>
     <row r="1799" spans="6:8">
       <c r="F1799" s="30"/>
-      <c r="G1799" s="30"/>
       <c r="H1799" s="30"/>
     </row>
     <row r="1800" spans="6:8">
       <c r="F1800" s="30"/>
-      <c r="G1800" s="30"/>
-      <c r="H1800" s="30"/>
+      <c r="H1800" s="53"/>
     </row>
     <row r="1801" spans="6:8">
       <c r="F1801" s="30"/>
-      <c r="G1801" s="30"/>
       <c r="H1801" s="30"/>
     </row>
     <row r="1802" spans="6:8">
       <c r="F1802" s="30"/>
-      <c r="G1802" s="30"/>
-      <c r="H1802" s="30"/>
+      <c r="H1802" s="53"/>
     </row>
     <row r="1803" spans="6:8">
       <c r="F1803" s="30"/>
-      <c r="G1803" s="30"/>
       <c r="H1803" s="30"/>
     </row>
     <row r="1804" spans="6:8">
-      <c r="F1804" s="30"/>
-      <c r="G1804" s="30"/>
-      <c r="H1804" s="30"/>
+      <c r="F1804" s="53"/>
+      <c r="H1804" s="53"/>
     </row>
     <row r="1805" spans="6:8">
       <c r="F1805" s="30"/>
@@ -21206,26 +21611,39 @@
       <c r="H1820" s="30"/>
     </row>
     <row r="1821" spans="6:8">
+      <c r="F1821" s="30"/>
       <c r="G1821" s="30"/>
+      <c r="H1821" s="30"/>
     </row>
     <row r="1822" spans="6:8">
       <c r="F1822" s="30"/>
       <c r="G1822" s="30"/>
+      <c r="H1822" s="30"/>
     </row>
     <row r="1823" spans="6:8">
+      <c r="F1823" s="30"/>
       <c r="G1823" s="30"/>
+      <c r="H1823" s="30"/>
     </row>
     <row r="1824" spans="6:8">
+      <c r="F1824" s="30"/>
       <c r="G1824" s="30"/>
+      <c r="H1824" s="30"/>
     </row>
     <row r="1825" spans="6:8">
+      <c r="F1825" s="30"/>
       <c r="G1825" s="30"/>
+      <c r="H1825" s="30"/>
     </row>
     <row r="1826" spans="6:8">
+      <c r="F1826" s="30"/>
       <c r="G1826" s="30"/>
+      <c r="H1826" s="30"/>
     </row>
     <row r="1827" spans="6:8">
+      <c r="F1827" s="30"/>
       <c r="G1827" s="30"/>
+      <c r="H1827" s="30"/>
     </row>
     <row r="1828" spans="6:8">
       <c r="F1828" s="30"/>
@@ -21233,118 +21651,142 @@
       <c r="H1828" s="30"/>
     </row>
     <row r="1829" spans="6:8">
+      <c r="F1829" s="30"/>
       <c r="G1829" s="30"/>
+      <c r="H1829" s="30"/>
     </row>
     <row r="1830" spans="6:8">
+      <c r="F1830" s="30"/>
       <c r="G1830" s="30"/>
+      <c r="H1830" s="30"/>
     </row>
     <row r="1831" spans="6:8">
+      <c r="F1831" s="30"/>
       <c r="G1831" s="30"/>
+      <c r="H1831" s="30"/>
     </row>
     <row r="1832" spans="6:8">
+      <c r="F1832" s="30"/>
       <c r="G1832" s="30"/>
+      <c r="H1832" s="30"/>
     </row>
     <row r="1833" spans="6:8">
+      <c r="F1833" s="30"/>
       <c r="G1833" s="30"/>
+      <c r="H1833" s="30"/>
     </row>
     <row r="1834" spans="6:8">
+      <c r="F1834" s="30"/>
       <c r="G1834" s="30"/>
+      <c r="H1834" s="30"/>
     </row>
     <row r="1835" spans="6:8">
+      <c r="F1835" s="30"/>
       <c r="G1835" s="30"/>
+      <c r="H1835" s="30"/>
     </row>
     <row r="1836" spans="6:8">
+      <c r="F1836" s="30"/>
       <c r="G1836" s="30"/>
+      <c r="H1836" s="30"/>
     </row>
     <row r="1837" spans="6:8">
+      <c r="F1837" s="30"/>
       <c r="G1837" s="30"/>
+      <c r="H1837" s="30"/>
     </row>
     <row r="1838" spans="6:8">
+      <c r="F1838" s="30"/>
       <c r="G1838" s="30"/>
-    </row>
-    <row r="1880" spans="6:6">
-      <c r="F1880" s="30"/>
-    </row>
-    <row r="1897" spans="6:8">
-      <c r="H1897" s="30"/>
-    </row>
-    <row r="1899" spans="6:8">
-      <c r="F1899" s="30"/>
-      <c r="H1899" s="30"/>
-    </row>
-    <row r="1900" spans="6:8">
-      <c r="F1900" s="30"/>
-      <c r="H1900" s="30"/>
-    </row>
-    <row r="1901" spans="6:8">
-      <c r="H1901" s="30"/>
-    </row>
-    <row r="1903" spans="6:8">
+      <c r="H1838" s="30"/>
+    </row>
+    <row r="1839" spans="6:8">
+      <c r="F1839" s="30"/>
+      <c r="G1839" s="30"/>
+      <c r="H1839" s="30"/>
+    </row>
+    <row r="1840" spans="6:8">
+      <c r="F1840" s="30"/>
+      <c r="G1840" s="30"/>
+      <c r="H1840" s="30"/>
+    </row>
+    <row r="1841" spans="6:8">
+      <c r="F1841" s="30"/>
+      <c r="G1841" s="30"/>
+      <c r="H1841" s="30"/>
+    </row>
+    <row r="1842" spans="6:8">
+      <c r="F1842" s="30"/>
+      <c r="G1842" s="30"/>
+      <c r="H1842" s="30"/>
+    </row>
+    <row r="1843" spans="6:8">
+      <c r="F1843" s="30"/>
+      <c r="G1843" s="30"/>
+      <c r="H1843" s="30"/>
+    </row>
+    <row r="1844" spans="6:8">
+      <c r="G1844" s="30"/>
+    </row>
+    <row r="1845" spans="6:8">
+      <c r="F1845" s="30"/>
+      <c r="G1845" s="30"/>
+    </row>
+    <row r="1846" spans="6:8">
+      <c r="G1846" s="30"/>
+    </row>
+    <row r="1847" spans="6:8">
+      <c r="G1847" s="30"/>
+    </row>
+    <row r="1848" spans="6:8">
+      <c r="G1848" s="30"/>
+    </row>
+    <row r="1849" spans="6:8">
+      <c r="G1849" s="30"/>
+    </row>
+    <row r="1850" spans="6:8">
+      <c r="G1850" s="30"/>
+    </row>
+    <row r="1851" spans="6:8">
+      <c r="F1851" s="30"/>
+      <c r="G1851" s="30"/>
+      <c r="H1851" s="30"/>
+    </row>
+    <row r="1852" spans="6:8">
+      <c r="G1852" s="30"/>
+    </row>
+    <row r="1853" spans="6:8">
+      <c r="G1853" s="30"/>
+    </row>
+    <row r="1854" spans="6:8">
+      <c r="G1854" s="30"/>
+    </row>
+    <row r="1855" spans="6:8">
+      <c r="G1855" s="30"/>
+    </row>
+    <row r="1856" spans="6:8">
+      <c r="G1856" s="30"/>
+    </row>
+    <row r="1857" spans="7:7">
+      <c r="G1857" s="30"/>
+    </row>
+    <row r="1858" spans="7:7">
+      <c r="G1858" s="30"/>
+    </row>
+    <row r="1859" spans="7:7">
+      <c r="G1859" s="30"/>
+    </row>
+    <row r="1860" spans="7:7">
+      <c r="G1860" s="30"/>
+    </row>
+    <row r="1861" spans="7:7">
+      <c r="G1861" s="30"/>
+    </row>
+    <row r="1903" spans="6:6">
       <c r="F1903" s="30"/>
-      <c r="H1903" s="30"/>
-    </row>
-    <row r="1904" spans="6:8">
-      <c r="F1904" s="30"/>
-      <c r="H1904" s="30"/>
-    </row>
-    <row r="1905" spans="6:8">
-      <c r="F1905" s="30"/>
-      <c r="H1905" s="30"/>
-    </row>
-    <row r="1906" spans="6:8">
-      <c r="F1906" s="30"/>
-      <c r="H1906" s="30"/>
-    </row>
-    <row r="1907" spans="6:8">
-      <c r="F1907" s="30"/>
-      <c r="H1907" s="30"/>
-    </row>
-    <row r="1908" spans="6:8">
-      <c r="F1908" s="30"/>
-      <c r="H1908" s="30"/>
-    </row>
-    <row r="1909" spans="6:8">
-      <c r="H1909" s="30"/>
-    </row>
-    <row r="1910" spans="6:8">
-      <c r="H1910" s="30"/>
-    </row>
-    <row r="1911" spans="6:8">
-      <c r="H1911" s="30"/>
-    </row>
-    <row r="1913" spans="6:8">
-      <c r="H1913" s="30"/>
-    </row>
-    <row r="1914" spans="6:8">
-      <c r="F1914" s="30"/>
-      <c r="H1914" s="30"/>
-    </row>
-    <row r="1915" spans="6:8">
-      <c r="F1915" s="30"/>
-      <c r="H1915" s="30"/>
-    </row>
-    <row r="1916" spans="6:8">
-      <c r="F1916" s="30"/>
-      <c r="H1916" s="30"/>
-    </row>
-    <row r="1917" spans="6:8">
-      <c r="F1917" s="30"/>
-      <c r="H1917" s="30"/>
-    </row>
-    <row r="1918" spans="6:8">
-      <c r="F1918" s="30"/>
-      <c r="H1918" s="30"/>
-    </row>
-    <row r="1919" spans="6:8">
-      <c r="F1919" s="30"/>
-      <c r="H1919" s="30"/>
-    </row>
-    <row r="1920" spans="6:8">
-      <c r="F1920" s="30"/>
+    </row>
+    <row r="1920" spans="8:8">
       <c r="H1920" s="30"/>
-    </row>
-    <row r="1921" spans="6:8">
-      <c r="H1921" s="30"/>
     </row>
     <row r="1922" spans="6:8">
       <c r="F1922" s="30"/>
@@ -21355,37 +21797,54 @@
       <c r="H1923" s="30"/>
     </row>
     <row r="1924" spans="6:8">
-      <c r="F1924" s="30"/>
       <c r="H1924" s="30"/>
     </row>
-    <row r="1925" spans="6:8">
-      <c r="F1925" s="30"/>
-      <c r="H1925" s="30"/>
+    <row r="1926" spans="6:8">
+      <c r="F1926" s="30"/>
+      <c r="H1926" s="30"/>
     </row>
     <row r="1927" spans="6:8">
+      <c r="F1927" s="30"/>
       <c r="H1927" s="30"/>
+    </row>
+    <row r="1928" spans="6:8">
+      <c r="F1928" s="30"/>
+      <c r="H1928" s="30"/>
     </row>
     <row r="1929" spans="6:8">
       <c r="F1929" s="30"/>
       <c r="H1929" s="30"/>
     </row>
+    <row r="1930" spans="6:8">
+      <c r="F1930" s="30"/>
+      <c r="H1930" s="30"/>
+    </row>
     <row r="1931" spans="6:8">
+      <c r="F1931" s="30"/>
       <c r="H1931" s="30"/>
+    </row>
+    <row r="1932" spans="6:8">
+      <c r="H1932" s="30"/>
     </row>
     <row r="1933" spans="6:8">
       <c r="H1933" s="30"/>
     </row>
-    <row r="1935" spans="6:8">
-      <c r="H1935" s="30"/>
+    <row r="1934" spans="6:8">
+      <c r="H1934" s="30"/>
     </row>
     <row r="1936" spans="6:8">
-      <c r="F1936" s="30"/>
       <c r="H1936" s="30"/>
     </row>
     <row r="1937" spans="6:8">
+      <c r="F1937" s="30"/>
       <c r="H1937" s="30"/>
     </row>
+    <row r="1938" spans="6:8">
+      <c r="F1938" s="30"/>
+      <c r="H1938" s="30"/>
+    </row>
     <row r="1939" spans="6:8">
+      <c r="F1939" s="30"/>
       <c r="H1939" s="30"/>
     </row>
     <row r="1940" spans="6:8">
@@ -21393,420 +21852,366 @@
       <c r="H1940" s="30"/>
     </row>
     <row r="1941" spans="6:8">
+      <c r="F1941" s="30"/>
       <c r="H1941" s="30"/>
     </row>
+    <row r="1942" spans="6:8">
+      <c r="F1942" s="30"/>
+      <c r="H1942" s="30"/>
+    </row>
     <row r="1943" spans="6:8">
+      <c r="F1943" s="30"/>
       <c r="H1943" s="30"/>
     </row>
+    <row r="1944" spans="6:8">
+      <c r="H1944" s="30"/>
+    </row>
     <row r="1945" spans="6:8">
+      <c r="F1945" s="30"/>
       <c r="H1945" s="30"/>
     </row>
+    <row r="1946" spans="6:8">
+      <c r="F1946" s="30"/>
+      <c r="H1946" s="30"/>
+    </row>
     <row r="1947" spans="6:8">
+      <c r="F1947" s="30"/>
       <c r="H1947" s="30"/>
     </row>
-    <row r="1949" spans="6:8">
-      <c r="H1949" s="30"/>
-    </row>
-    <row r="1951" spans="6:8">
-      <c r="F1951" s="30"/>
-      <c r="H1951" s="30"/>
-    </row>
-    <row r="1961" spans="6:6">
-      <c r="F1961" s="30"/>
-    </row>
-    <row r="1978" spans="6:8">
-      <c r="H1978" s="30"/>
-    </row>
-    <row r="1980" spans="6:8">
-      <c r="H1980" s="30"/>
-    </row>
-    <row r="1982" spans="6:8">
-      <c r="F1982" s="30"/>
-      <c r="H1982" s="30"/>
+    <row r="1948" spans="6:8">
+      <c r="F1948" s="30"/>
+      <c r="H1948" s="30"/>
+    </row>
+    <row r="1950" spans="6:8">
+      <c r="H1950" s="30"/>
+    </row>
+    <row r="1952" spans="6:8">
+      <c r="F1952" s="30"/>
+      <c r="H1952" s="30"/>
+    </row>
+    <row r="1954" spans="6:8">
+      <c r="H1954" s="30"/>
+    </row>
+    <row r="1956" spans="6:8">
+      <c r="H1956" s="30"/>
+    </row>
+    <row r="1958" spans="6:8">
+      <c r="H1958" s="30"/>
+    </row>
+    <row r="1959" spans="6:8">
+      <c r="F1959" s="30"/>
+      <c r="H1959" s="30"/>
+    </row>
+    <row r="1960" spans="6:8">
+      <c r="H1960" s="30"/>
+    </row>
+    <row r="1962" spans="6:8">
+      <c r="H1962" s="30"/>
+    </row>
+    <row r="1963" spans="6:8">
+      <c r="F1963" s="30"/>
+      <c r="H1963" s="30"/>
+    </row>
+    <row r="1964" spans="6:8">
+      <c r="H1964" s="30"/>
+    </row>
+    <row r="1966" spans="6:8">
+      <c r="H1966" s="30"/>
+    </row>
+    <row r="1968" spans="6:8">
+      <c r="H1968" s="30"/>
+    </row>
+    <row r="1970" spans="6:8">
+      <c r="H1970" s="30"/>
+    </row>
+    <row r="1972" spans="6:8">
+      <c r="H1972" s="30"/>
+    </row>
+    <row r="1974" spans="6:8">
+      <c r="F1974" s="30"/>
+      <c r="H1974" s="30"/>
     </row>
     <row r="1984" spans="6:8">
-      <c r="H1984" s="30"/>
-    </row>
-    <row r="1986" spans="6:8">
-      <c r="H1986" s="30"/>
-    </row>
-    <row r="1988" spans="6:8">
-      <c r="H1988" s="30"/>
-    </row>
-    <row r="1990" spans="6:8">
-      <c r="H1990" s="30"/>
-    </row>
-    <row r="1991" spans="6:8">
-      <c r="F1991" s="30"/>
-      <c r="H1991" s="30"/>
-    </row>
-    <row r="1992" spans="6:8">
-      <c r="H1992" s="30"/>
-    </row>
-    <row r="1994" spans="6:8">
-      <c r="H1994" s="30"/>
-    </row>
-    <row r="1996" spans="6:8">
-      <c r="H1996" s="30"/>
-    </row>
-    <row r="1998" spans="6:8">
-      <c r="H1998" s="30"/>
-    </row>
-    <row r="1999" spans="6:8">
-      <c r="F1999" s="30"/>
-      <c r="H1999" s="30"/>
-    </row>
-    <row r="2000" spans="6:8">
-      <c r="H2000" s="30"/>
-    </row>
-    <row r="2002" spans="6:8">
-      <c r="H2002" s="30"/>
-    </row>
-    <row r="2004" spans="6:8">
-      <c r="H2004" s="30"/>
-    </row>
-    <row r="2006" spans="6:8">
-      <c r="H2006" s="30"/>
-    </row>
-    <row r="2008" spans="6:8">
-      <c r="F2008" s="30"/>
-      <c r="H2008" s="30"/>
-    </row>
-    <row r="2016" spans="6:8">
-      <c r="F2016" s="30"/>
-    </row>
-    <row r="2024" spans="6:8">
-      <c r="F2024" s="30"/>
+      <c r="F1984" s="30"/>
+    </row>
+    <row r="2001" spans="6:8">
+      <c r="H2001" s="30"/>
+    </row>
+    <row r="2003" spans="6:8">
+      <c r="H2003" s="30"/>
+    </row>
+    <row r="2005" spans="6:8">
+      <c r="F2005" s="30"/>
+      <c r="H2005" s="30"/>
+    </row>
+    <row r="2007" spans="6:8">
+      <c r="H2007" s="30"/>
+    </row>
+    <row r="2009" spans="6:8">
+      <c r="H2009" s="30"/>
+    </row>
+    <row r="2011" spans="6:8">
+      <c r="H2011" s="30"/>
+    </row>
+    <row r="2013" spans="6:8">
+      <c r="H2013" s="30"/>
+    </row>
+    <row r="2014" spans="6:8">
+      <c r="F2014" s="30"/>
+      <c r="H2014" s="30"/>
+    </row>
+    <row r="2015" spans="6:8">
+      <c r="H2015" s="30"/>
+    </row>
+    <row r="2017" spans="6:8">
+      <c r="H2017" s="30"/>
+    </row>
+    <row r="2019" spans="6:8">
+      <c r="H2019" s="30"/>
+    </row>
+    <row r="2021" spans="6:8">
+      <c r="H2021" s="30"/>
+    </row>
+    <row r="2022" spans="6:8">
+      <c r="F2022" s="30"/>
+      <c r="H2022" s="30"/>
+    </row>
+    <row r="2023" spans="6:8">
+      <c r="H2023" s="30"/>
+    </row>
+    <row r="2025" spans="6:8">
+      <c r="H2025" s="30"/>
+    </row>
+    <row r="2027" spans="6:8">
+      <c r="H2027" s="30"/>
+    </row>
+    <row r="2029" spans="6:8">
+      <c r="H2029" s="30"/>
     </row>
     <row r="2031" spans="6:8">
       <c r="F2031" s="30"/>
       <c r="H2031" s="30"/>
     </row>
-    <row r="2047" spans="6:8">
-      <c r="F2047" s="54"/>
-      <c r="H2047" s="54"/>
-    </row>
-    <row r="2048" spans="6:8">
-      <c r="F2048" s="54"/>
-    </row>
-    <row r="2051" spans="6:8">
-      <c r="F2051" s="54"/>
-      <c r="H2051" s="54"/>
-    </row>
-    <row r="2052" spans="6:8">
-      <c r="F2052" s="30"/>
-    </row>
-    <row r="2065" spans="6:8">
-      <c r="F2065" s="30"/>
-      <c r="H2065" s="30"/>
-    </row>
-    <row r="2080" spans="6:8">
-      <c r="F2080" s="54"/>
-      <c r="H2080" s="54"/>
-    </row>
-    <row r="2081" spans="6:8">
-      <c r="F2081" s="54"/>
-    </row>
-    <row r="2084" spans="6:8">
-      <c r="F2084" s="54"/>
-      <c r="H2084" s="54"/>
-    </row>
-    <row r="2085" spans="6:8">
-      <c r="F2085" s="30"/>
-    </row>
-    <row r="2098" spans="6:8">
-      <c r="F2098" s="30"/>
-      <c r="H2098" s="30"/>
-    </row>
-    <row r="2113" spans="6:8">
-      <c r="F2113" s="54"/>
-      <c r="H2113" s="54"/>
-    </row>
-    <row r="2114" spans="6:8">
-      <c r="F2114" s="54"/>
-    </row>
-    <row r="2117" spans="6:8">
-      <c r="F2117" s="54"/>
-      <c r="H2117" s="54"/>
-    </row>
-    <row r="2118" spans="6:8">
-      <c r="F2118" s="30"/>
-    </row>
-    <row r="2131" spans="6:8">
-      <c r="F2131" s="30"/>
-      <c r="H2131" s="30"/>
-    </row>
-    <row r="2139" spans="6:8">
-      <c r="F2139" s="30"/>
-      <c r="G2139" s="30"/>
-      <c r="H2139" s="30"/>
-    </row>
-    <row r="2146" spans="6:8">
-      <c r="F2146" s="54"/>
-      <c r="H2146" s="54"/>
-    </row>
-    <row r="2147" spans="6:8">
-      <c r="F2147" s="54"/>
-    </row>
-    <row r="2150" spans="6:8">
-      <c r="F2150" s="54"/>
-      <c r="H2150" s="54"/>
-    </row>
-    <row r="2151" spans="6:8">
-      <c r="F2151" s="30"/>
-    </row>
-    <row r="2164" spans="6:8">
-      <c r="F2164" s="30"/>
-      <c r="H2164" s="30"/>
-    </row>
-    <row r="2172" spans="6:8">
-      <c r="F2172" s="30"/>
-      <c r="G2172" s="30"/>
-      <c r="H2172" s="30"/>
-    </row>
-    <row r="2179" spans="6:8">
-      <c r="F2179" s="54"/>
-      <c r="H2179" s="54"/>
-    </row>
-    <row r="2180" spans="6:8">
-      <c r="F2180" s="54"/>
-    </row>
-    <row r="2183" spans="6:8">
-      <c r="F2183" s="54"/>
-      <c r="H2183" s="54"/>
-    </row>
-    <row r="2184" spans="6:8">
-      <c r="F2184" s="30"/>
-    </row>
-    <row r="2197" spans="6:8">
-      <c r="F2197" s="30"/>
-      <c r="H2197" s="30"/>
-    </row>
-    <row r="2205" spans="6:8">
-      <c r="F2205" s="30"/>
-      <c r="G2205" s="30"/>
-      <c r="H2205" s="30"/>
-    </row>
-    <row r="2212" spans="6:8">
-      <c r="F2212" s="54"/>
-      <c r="H2212" s="54"/>
-    </row>
-    <row r="2213" spans="6:8">
-      <c r="F2213" s="54"/>
-    </row>
-    <row r="2216" spans="6:8">
-      <c r="F2216" s="54"/>
-      <c r="H2216" s="54"/>
-    </row>
-    <row r="2217" spans="6:8">
-      <c r="F2217" s="30"/>
-    </row>
-    <row r="2230" spans="6:8">
-      <c r="F2230" s="30"/>
-      <c r="H2230" s="30"/>
-    </row>
-    <row r="2245" spans="6:8">
-      <c r="F2245" s="54"/>
-      <c r="H2245" s="54"/>
-    </row>
-    <row r="2246" spans="6:8">
-      <c r="F2246" s="54"/>
-    </row>
-    <row r="2249" spans="6:8">
-      <c r="F2249" s="54"/>
-      <c r="H2249" s="54"/>
-    </row>
-    <row r="2250" spans="6:8">
-      <c r="F2250" s="30"/>
-    </row>
-    <row r="2263" spans="6:8">
-      <c r="F2263" s="30"/>
-      <c r="H2263" s="30"/>
-    </row>
-    <row r="2278" spans="6:8">
-      <c r="F2278" s="54"/>
-      <c r="H2278" s="54"/>
-    </row>
-    <row r="2279" spans="6:8">
-      <c r="F2279" s="54"/>
-    </row>
-    <row r="2282" spans="6:8">
-      <c r="F2282" s="54"/>
-      <c r="H2282" s="54"/>
-    </row>
-    <row r="2283" spans="6:8">
-      <c r="F2283" s="30"/>
-    </row>
-    <row r="2296" spans="6:8">
-      <c r="F2296" s="30"/>
-      <c r="H2296" s="30"/>
-    </row>
-    <row r="2304" spans="6:8">
-      <c r="F2304" s="30"/>
-      <c r="G2304" s="30"/>
-      <c r="H2304" s="30"/>
-    </row>
-    <row r="2311" spans="6:8">
-      <c r="F2311" s="54"/>
-      <c r="H2311" s="54"/>
-    </row>
-    <row r="2312" spans="6:8">
-      <c r="F2312" s="54"/>
-    </row>
-    <row r="2315" spans="6:8">
-      <c r="F2315" s="54"/>
-      <c r="H2315" s="54"/>
-    </row>
-    <row r="2316" spans="6:8">
-      <c r="F2316" s="30"/>
-    </row>
-    <row r="2329" spans="6:8">
-      <c r="F2329" s="30"/>
-      <c r="H2329" s="30"/>
-    </row>
-    <row r="2337" spans="6:8">
-      <c r="F2337" s="30"/>
-      <c r="G2337" s="30"/>
-      <c r="H2337" s="30"/>
-    </row>
-    <row r="2344" spans="6:8">
-      <c r="F2344" s="54"/>
-      <c r="H2344" s="54"/>
-    </row>
-    <row r="2345" spans="6:8">
-      <c r="F2345" s="54"/>
-    </row>
-    <row r="2348" spans="6:8">
-      <c r="F2348" s="54"/>
-      <c r="H2348" s="54"/>
-    </row>
-    <row r="2349" spans="6:8">
-      <c r="F2349" s="30"/>
-    </row>
-    <row r="2362" spans="6:8">
-      <c r="F2362" s="30"/>
-      <c r="H2362" s="30"/>
-    </row>
-    <row r="2370" spans="6:8">
-      <c r="F2370" s="30"/>
-      <c r="G2370" s="30"/>
-      <c r="H2370" s="30"/>
+    <row r="2039" spans="6:6">
+      <c r="F2039" s="30"/>
+    </row>
+    <row r="2047" spans="6:6">
+      <c r="F2047" s="30"/>
+    </row>
+    <row r="2054" spans="6:8">
+      <c r="F2054" s="30"/>
+      <c r="H2054" s="30"/>
+    </row>
+    <row r="2070" spans="6:8">
+      <c r="F2070" s="54"/>
+      <c r="H2070" s="54"/>
+    </row>
+    <row r="2071" spans="6:8">
+      <c r="F2071" s="54"/>
+    </row>
+    <row r="2074" spans="6:8">
+      <c r="F2074" s="54"/>
+      <c r="H2074" s="54"/>
+    </row>
+    <row r="2075" spans="6:8">
+      <c r="F2075" s="30"/>
+    </row>
+    <row r="2088" spans="6:8">
+      <c r="F2088" s="30"/>
+      <c r="H2088" s="30"/>
+    </row>
+    <row r="2103" spans="6:8">
+      <c r="F2103" s="54"/>
+      <c r="H2103" s="54"/>
+    </row>
+    <row r="2104" spans="6:8">
+      <c r="F2104" s="54"/>
+    </row>
+    <row r="2107" spans="6:8">
+      <c r="F2107" s="54"/>
+      <c r="H2107" s="54"/>
+    </row>
+    <row r="2108" spans="6:8">
+      <c r="F2108" s="30"/>
+    </row>
+    <row r="2121" spans="6:8">
+      <c r="F2121" s="30"/>
+      <c r="H2121" s="30"/>
+    </row>
+    <row r="2136" spans="6:8">
+      <c r="F2136" s="54"/>
+      <c r="H2136" s="54"/>
+    </row>
+    <row r="2137" spans="6:8">
+      <c r="F2137" s="54"/>
+    </row>
+    <row r="2140" spans="6:8">
+      <c r="F2140" s="54"/>
+      <c r="H2140" s="54"/>
+    </row>
+    <row r="2141" spans="6:8">
+      <c r="F2141" s="30"/>
+    </row>
+    <row r="2154" spans="6:8">
+      <c r="F2154" s="30"/>
+      <c r="H2154" s="30"/>
+    </row>
+    <row r="2162" spans="6:8">
+      <c r="F2162" s="30"/>
+      <c r="G2162" s="30"/>
+      <c r="H2162" s="30"/>
+    </row>
+    <row r="2169" spans="6:8">
+      <c r="F2169" s="54"/>
+      <c r="H2169" s="54"/>
+    </row>
+    <row r="2170" spans="6:8">
+      <c r="F2170" s="54"/>
+    </row>
+    <row r="2173" spans="6:8">
+      <c r="F2173" s="54"/>
+      <c r="H2173" s="54"/>
+    </row>
+    <row r="2174" spans="6:8">
+      <c r="F2174" s="30"/>
+    </row>
+    <row r="2187" spans="6:8">
+      <c r="F2187" s="30"/>
+      <c r="H2187" s="30"/>
+    </row>
+    <row r="2195" spans="6:8">
+      <c r="F2195" s="30"/>
+      <c r="G2195" s="30"/>
+      <c r="H2195" s="30"/>
+    </row>
+    <row r="2202" spans="6:8">
+      <c r="F2202" s="54"/>
+      <c r="H2202" s="54"/>
+    </row>
+    <row r="2203" spans="6:8">
+      <c r="F2203" s="54"/>
+    </row>
+    <row r="2206" spans="6:8">
+      <c r="F2206" s="54"/>
+      <c r="H2206" s="54"/>
+    </row>
+    <row r="2207" spans="6:8">
+      <c r="F2207" s="30"/>
+    </row>
+    <row r="2220" spans="6:8">
+      <c r="F2220" s="30"/>
+      <c r="H2220" s="30"/>
+    </row>
+    <row r="2228" spans="6:8">
+      <c r="F2228" s="30"/>
+      <c r="G2228" s="30"/>
+      <c r="H2228" s="30"/>
+    </row>
+    <row r="2235" spans="6:8">
+      <c r="F2235" s="54"/>
+      <c r="H2235" s="54"/>
+    </row>
+    <row r="2236" spans="6:8">
+      <c r="F2236" s="54"/>
+    </row>
+    <row r="2239" spans="6:8">
+      <c r="F2239" s="54"/>
+      <c r="H2239" s="54"/>
+    </row>
+    <row r="2240" spans="6:8">
+      <c r="F2240" s="30"/>
+    </row>
+    <row r="2253" spans="6:8">
+      <c r="F2253" s="30"/>
+      <c r="H2253" s="30"/>
+    </row>
+    <row r="2268" spans="6:8">
+      <c r="F2268" s="54"/>
+      <c r="H2268" s="54"/>
+    </row>
+    <row r="2269" spans="6:8">
+      <c r="F2269" s="54"/>
+    </row>
+    <row r="2272" spans="6:8">
+      <c r="F2272" s="54"/>
+      <c r="H2272" s="54"/>
+    </row>
+    <row r="2273" spans="6:8">
+      <c r="F2273" s="30"/>
+    </row>
+    <row r="2286" spans="6:8">
+      <c r="F2286" s="30"/>
+      <c r="H2286" s="30"/>
+    </row>
+    <row r="2301" spans="6:8">
+      <c r="F2301" s="54"/>
+      <c r="H2301" s="54"/>
+    </row>
+    <row r="2302" spans="6:8">
+      <c r="F2302" s="54"/>
+    </row>
+    <row r="2305" spans="6:8">
+      <c r="F2305" s="54"/>
+      <c r="H2305" s="54"/>
+    </row>
+    <row r="2306" spans="6:8">
+      <c r="F2306" s="30"/>
+    </row>
+    <row r="2319" spans="6:8">
+      <c r="F2319" s="30"/>
+      <c r="H2319" s="30"/>
+    </row>
+    <row r="2327" spans="6:8">
+      <c r="F2327" s="30"/>
+      <c r="G2327" s="30"/>
+      <c r="H2327" s="30"/>
+    </row>
+    <row r="2334" spans="6:8">
+      <c r="F2334" s="54"/>
+      <c r="H2334" s="54"/>
+    </row>
+    <row r="2335" spans="6:8">
+      <c r="F2335" s="54"/>
+    </row>
+    <row r="2338" spans="6:8">
+      <c r="F2338" s="54"/>
+      <c r="H2338" s="54"/>
+    </row>
+    <row r="2339" spans="6:8">
+      <c r="F2339" s="30"/>
+    </row>
+    <row r="2352" spans="6:8">
+      <c r="F2352" s="30"/>
+      <c r="H2352" s="30"/>
+    </row>
+    <row r="2360" spans="6:8">
+      <c r="F2360" s="30"/>
+      <c r="G2360" s="30"/>
+      <c r="H2360" s="30"/>
+    </row>
+    <row r="2367" spans="6:8">
+      <c r="F2367" s="54"/>
+      <c r="H2367" s="54"/>
+    </row>
+    <row r="2368" spans="6:8">
+      <c r="F2368" s="54"/>
+    </row>
+    <row r="2371" spans="6:8">
+      <c r="F2371" s="54"/>
+      <c r="H2371" s="54"/>
     </row>
     <row r="2372" spans="6:8">
       <c r="F2372" s="30"/>
-      <c r="G2372" s="30"/>
-      <c r="H2372" s="30"/>
-    </row>
-    <row r="2373" spans="6:8">
-      <c r="F2373" s="30"/>
-      <c r="G2373" s="30"/>
-      <c r="H2373" s="30"/>
-    </row>
-    <row r="2374" spans="6:8">
-      <c r="F2374" s="30"/>
-      <c r="G2374" s="30"/>
-      <c r="H2374" s="30"/>
-    </row>
-    <row r="2375" spans="6:8">
-      <c r="F2375" s="30"/>
-      <c r="G2375" s="30"/>
-      <c r="H2375" s="30"/>
-    </row>
-    <row r="2376" spans="6:8">
-      <c r="F2376" s="30"/>
-      <c r="G2376" s="30"/>
-      <c r="H2376" s="30"/>
-    </row>
-    <row r="2377" spans="6:8">
-      <c r="F2377" s="30"/>
-      <c r="G2377" s="30"/>
-      <c r="H2377" s="30"/>
-    </row>
-    <row r="2378" spans="6:8">
-      <c r="F2378" s="30"/>
-      <c r="G2378" s="30"/>
-      <c r="H2378" s="30"/>
-    </row>
-    <row r="2379" spans="6:8">
-      <c r="F2379" s="30"/>
-      <c r="G2379" s="30"/>
-      <c r="H2379" s="30"/>
-    </row>
-    <row r="2380" spans="6:8">
-      <c r="F2380" s="30"/>
-      <c r="G2380" s="30"/>
-      <c r="H2380" s="30"/>
-    </row>
-    <row r="2381" spans="6:8">
-      <c r="F2381" s="30"/>
-      <c r="G2381" s="30"/>
-      <c r="H2381" s="30"/>
-    </row>
-    <row r="2382" spans="6:8">
-      <c r="F2382" s="30"/>
-      <c r="G2382" s="30"/>
-      <c r="H2382" s="30"/>
-    </row>
-    <row r="2383" spans="6:8">
-      <c r="F2383" s="30"/>
-      <c r="G2383" s="30"/>
-      <c r="H2383" s="30"/>
-    </row>
-    <row r="2384" spans="6:8">
-      <c r="F2384" s="30"/>
-      <c r="G2384" s="30"/>
-      <c r="H2384" s="30"/>
     </row>
     <row r="2385" spans="6:8">
       <c r="F2385" s="30"/>
-      <c r="G2385" s="30"/>
       <c r="H2385" s="30"/>
-    </row>
-    <row r="2386" spans="6:8">
-      <c r="F2386" s="30"/>
-      <c r="G2386" s="30"/>
-      <c r="H2386" s="30"/>
-    </row>
-    <row r="2387" spans="6:8">
-      <c r="F2387" s="30"/>
-      <c r="G2387" s="30"/>
-      <c r="H2387" s="30"/>
-    </row>
-    <row r="2388" spans="6:8">
-      <c r="F2388" s="30"/>
-      <c r="G2388" s="30"/>
-      <c r="H2388" s="30"/>
-    </row>
-    <row r="2389" spans="6:8">
-      <c r="F2389" s="30"/>
-      <c r="G2389" s="30"/>
-      <c r="H2389" s="30"/>
-    </row>
-    <row r="2390" spans="6:8">
-      <c r="F2390" s="30"/>
-      <c r="G2390" s="30"/>
-      <c r="H2390" s="30"/>
-    </row>
-    <row r="2391" spans="6:8">
-      <c r="F2391" s="30"/>
-      <c r="G2391" s="30"/>
-      <c r="H2391" s="30"/>
-    </row>
-    <row r="2392" spans="6:8">
-      <c r="F2392" s="30"/>
-      <c r="G2392" s="30"/>
-      <c r="H2392" s="30"/>
     </row>
     <row r="2393" spans="6:8">
       <c r="F2393" s="30"/>
       <c r="G2393" s="30"/>
       <c r="H2393" s="30"/>
     </row>
-    <row r="2394" spans="6:8">
-      <c r="F2394" s="30"/>
-      <c r="G2394" s="30"/>
-      <c r="H2394" s="30"/>
-    </row>
     <row r="2395" spans="6:8">
       <c r="F2395" s="30"/>
       <c r="G2395" s="30"/>
@@ -21832,220 +22237,335 @@
       <c r="G2399" s="30"/>
       <c r="H2399" s="30"/>
     </row>
+    <row r="2400" spans="6:8">
+      <c r="F2400" s="30"/>
+      <c r="G2400" s="30"/>
+      <c r="H2400" s="30"/>
+    </row>
     <row r="2401" spans="6:8">
       <c r="F2401" s="30"/>
       <c r="G2401" s="30"/>
       <c r="H2401" s="30"/>
     </row>
+    <row r="2402" spans="6:8">
+      <c r="F2402" s="30"/>
+      <c r="G2402" s="30"/>
+      <c r="H2402" s="30"/>
+    </row>
+    <row r="2403" spans="6:8">
+      <c r="F2403" s="30"/>
+      <c r="G2403" s="30"/>
+      <c r="H2403" s="30"/>
+    </row>
+    <row r="2404" spans="6:8">
+      <c r="F2404" s="30"/>
+      <c r="G2404" s="30"/>
+      <c r="H2404" s="30"/>
+    </row>
+    <row r="2405" spans="6:8">
+      <c r="F2405" s="30"/>
+      <c r="G2405" s="30"/>
+      <c r="H2405" s="30"/>
+    </row>
+    <row r="2406" spans="6:8">
+      <c r="F2406" s="30"/>
+      <c r="G2406" s="30"/>
+      <c r="H2406" s="30"/>
+    </row>
+    <row r="2407" spans="6:8">
+      <c r="F2407" s="30"/>
+      <c r="G2407" s="30"/>
+      <c r="H2407" s="30"/>
+    </row>
+    <row r="2408" spans="6:8">
+      <c r="F2408" s="30"/>
+      <c r="G2408" s="30"/>
+      <c r="H2408" s="30"/>
+    </row>
+    <row r="2409" spans="6:8">
+      <c r="F2409" s="30"/>
+      <c r="G2409" s="30"/>
+      <c r="H2409" s="30"/>
+    </row>
+    <row r="2410" spans="6:8">
+      <c r="F2410" s="30"/>
+      <c r="G2410" s="30"/>
+      <c r="H2410" s="30"/>
+    </row>
+    <row r="2411" spans="6:8">
+      <c r="F2411" s="30"/>
+      <c r="G2411" s="30"/>
+      <c r="H2411" s="30"/>
+    </row>
+    <row r="2412" spans="6:8">
+      <c r="F2412" s="30"/>
+      <c r="G2412" s="30"/>
+      <c r="H2412" s="30"/>
+    </row>
+    <row r="2413" spans="6:8">
+      <c r="F2413" s="30"/>
+      <c r="G2413" s="30"/>
+      <c r="H2413" s="30"/>
+    </row>
     <row r="2414" spans="6:8">
       <c r="F2414" s="30"/>
       <c r="G2414" s="30"/>
       <c r="H2414" s="30"/>
     </row>
-    <row r="2428" spans="6:8">
-      <c r="F2428" s="30"/>
-      <c r="G2428" s="30"/>
-      <c r="H2428" s="30"/>
-    </row>
-    <row r="2430" spans="6:8">
-      <c r="F2430" s="30"/>
-      <c r="G2430" s="30"/>
-      <c r="H2430" s="30"/>
-    </row>
-    <row r="2443" spans="6:8">
-      <c r="F2443" s="30"/>
-      <c r="G2443" s="30"/>
-      <c r="H2443" s="30"/>
-    </row>
-    <row r="2457" spans="6:8">
-      <c r="F2457" s="30"/>
-      <c r="G2457" s="30"/>
-      <c r="H2457" s="30"/>
-    </row>
-    <row r="2459" spans="6:8">
-      <c r="F2459" s="30"/>
-      <c r="G2459" s="30"/>
-      <c r="H2459" s="30"/>
-    </row>
-    <row r="2472" spans="6:8">
-      <c r="F2472" s="30"/>
-      <c r="G2472" s="30"/>
-      <c r="H2472" s="30"/>
-    </row>
-    <row r="2486" spans="6:8">
-      <c r="F2486" s="30"/>
-      <c r="G2486" s="30"/>
-      <c r="H2486" s="30"/>
-    </row>
-    <row r="2489" spans="6:8">
-      <c r="F2489" s="30"/>
-      <c r="G2489" s="30"/>
-      <c r="H2489" s="30"/>
-    </row>
-    <row r="2490" spans="6:8">
-      <c r="F2490" s="30"/>
-      <c r="G2490" s="30"/>
-      <c r="H2490" s="30"/>
-    </row>
-    <row r="2491" spans="6:8">
-      <c r="F2491" s="30"/>
-      <c r="G2491" s="30"/>
-      <c r="H2491" s="30"/>
-    </row>
-    <row r="2492" spans="6:8">
-      <c r="F2492" s="30"/>
-      <c r="G2492" s="30"/>
-      <c r="H2492" s="30"/>
-    </row>
-    <row r="2493" spans="6:8">
-      <c r="F2493" s="30"/>
-      <c r="G2493" s="30"/>
-      <c r="H2493" s="30"/>
-    </row>
-    <row r="2494" spans="6:8">
-      <c r="F2494" s="30"/>
-      <c r="G2494" s="30"/>
-      <c r="H2494" s="30"/>
+    <row r="2415" spans="6:8">
+      <c r="F2415" s="30"/>
+      <c r="G2415" s="30"/>
+      <c r="H2415" s="30"/>
+    </row>
+    <row r="2416" spans="6:8">
+      <c r="F2416" s="30"/>
+      <c r="G2416" s="30"/>
+      <c r="H2416" s="30"/>
+    </row>
+    <row r="2417" spans="6:8">
+      <c r="F2417" s="30"/>
+      <c r="G2417" s="30"/>
+      <c r="H2417" s="30"/>
+    </row>
+    <row r="2418" spans="6:8">
+      <c r="F2418" s="30"/>
+      <c r="G2418" s="30"/>
+      <c r="H2418" s="30"/>
+    </row>
+    <row r="2419" spans="6:8">
+      <c r="F2419" s="30"/>
+      <c r="G2419" s="30"/>
+      <c r="H2419" s="30"/>
+    </row>
+    <row r="2420" spans="6:8">
+      <c r="F2420" s="30"/>
+      <c r="G2420" s="30"/>
+      <c r="H2420" s="30"/>
+    </row>
+    <row r="2421" spans="6:8">
+      <c r="F2421" s="30"/>
+      <c r="G2421" s="30"/>
+      <c r="H2421" s="30"/>
+    </row>
+    <row r="2422" spans="6:8">
+      <c r="F2422" s="30"/>
+      <c r="G2422" s="30"/>
+      <c r="H2422" s="30"/>
+    </row>
+    <row r="2424" spans="6:8">
+      <c r="F2424" s="30"/>
+      <c r="G2424" s="30"/>
+      <c r="H2424" s="30"/>
+    </row>
+    <row r="2437" spans="6:8">
+      <c r="F2437" s="30"/>
+      <c r="G2437" s="30"/>
+      <c r="H2437" s="30"/>
+    </row>
+    <row r="2451" spans="6:8">
+      <c r="F2451" s="30"/>
+      <c r="G2451" s="30"/>
+      <c r="H2451" s="30"/>
+    </row>
+    <row r="2453" spans="6:8">
+      <c r="F2453" s="30"/>
+      <c r="G2453" s="30"/>
+      <c r="H2453" s="30"/>
+    </row>
+    <row r="2466" spans="6:8">
+      <c r="F2466" s="30"/>
+      <c r="G2466" s="30"/>
+      <c r="H2466" s="30"/>
+    </row>
+    <row r="2480" spans="6:8">
+      <c r="F2480" s="30"/>
+      <c r="G2480" s="30"/>
+      <c r="H2480" s="30"/>
+    </row>
+    <row r="2482" spans="6:8">
+      <c r="F2482" s="30"/>
+      <c r="G2482" s="30"/>
+      <c r="H2482" s="30"/>
     </row>
     <row r="2495" spans="6:8">
       <c r="F2495" s="30"/>
       <c r="G2495" s="30"/>
       <c r="H2495" s="30"/>
     </row>
-    <row r="2496" spans="6:8">
-      <c r="F2496" s="30"/>
-      <c r="G2496" s="30"/>
-      <c r="H2496" s="30"/>
-    </row>
-    <row r="2497" spans="6:8">
-      <c r="F2497" s="30"/>
-      <c r="G2497" s="30"/>
-      <c r="H2497" s="30"/>
-    </row>
-    <row r="2498" spans="6:8">
-      <c r="F2498" s="30"/>
-      <c r="G2498" s="30"/>
-      <c r="H2498" s="30"/>
-    </row>
-    <row r="2499" spans="6:8">
-      <c r="F2499" s="30"/>
-      <c r="G2499" s="30"/>
-      <c r="H2499" s="30"/>
-    </row>
-    <row r="2500" spans="6:8">
-      <c r="F2500" s="30"/>
-      <c r="G2500" s="30"/>
-      <c r="H2500" s="30"/>
-    </row>
-    <row r="2501" spans="6:8">
-      <c r="F2501" s="30"/>
-      <c r="G2501" s="30"/>
-      <c r="H2501" s="30"/>
-    </row>
-    <row r="2502" spans="6:8">
-      <c r="F2502" s="30"/>
-      <c r="G2502" s="30"/>
-      <c r="H2502" s="30"/>
-    </row>
-    <row r="2511" spans="6:8">
-      <c r="F2511" s="30"/>
-      <c r="G2511" s="30"/>
-      <c r="H2511" s="30"/>
-    </row>
-    <row r="2528" spans="6:8">
-      <c r="F2528" s="30"/>
-      <c r="G2528" s="30"/>
-      <c r="H2528" s="30"/>
-    </row>
-    <row r="2545" spans="6:8">
-      <c r="F2545" s="30"/>
-      <c r="G2545" s="30"/>
-      <c r="H2545" s="30"/>
-    </row>
-    <row r="2562" spans="6:8">
-      <c r="F2562" s="30"/>
-      <c r="G2562" s="30"/>
-      <c r="H2562" s="30"/>
-    </row>
-    <row r="2579" spans="6:6">
-      <c r="F2579" s="30"/>
-    </row>
-    <row r="2596" spans="6:6">
-      <c r="F2596" s="30"/>
-    </row>
-    <row r="2613" spans="6:6">
-      <c r="F2613" s="30"/>
-    </row>
-    <row r="2630" spans="6:6">
-      <c r="F2630" s="30"/>
-    </row>
-    <row r="2647" spans="6:6">
-      <c r="F2647" s="30"/>
-    </row>
-    <row r="2664" spans="6:6">
-      <c r="F2664" s="30"/>
-    </row>
-    <row r="2681" spans="6:6">
-      <c r="F2681" s="30"/>
-    </row>
-    <row r="2698" spans="6:8">
-      <c r="F2698" s="30"/>
-      <c r="H2698" s="30"/>
-    </row>
-    <row r="2715" spans="6:6">
-      <c r="F2715" s="30"/>
-    </row>
-    <row r="2749" spans="6:6">
-      <c r="F2749" s="30"/>
-    </row>
-    <row r="2766" spans="6:6">
-      <c r="F2766" s="30"/>
-    </row>
-    <row r="2789" spans="6:8">
+    <row r="2509" spans="6:8">
+      <c r="F2509" s="30"/>
+      <c r="G2509" s="30"/>
+      <c r="H2509" s="30"/>
+    </row>
+    <row r="2512" spans="6:8">
+      <c r="F2512" s="30"/>
+      <c r="G2512" s="30"/>
+      <c r="H2512" s="30"/>
+    </row>
+    <row r="2513" spans="6:8">
+      <c r="F2513" s="30"/>
+      <c r="G2513" s="30"/>
+      <c r="H2513" s="30"/>
+    </row>
+    <row r="2514" spans="6:8">
+      <c r="F2514" s="30"/>
+      <c r="G2514" s="30"/>
+      <c r="H2514" s="30"/>
+    </row>
+    <row r="2515" spans="6:8">
+      <c r="F2515" s="30"/>
+      <c r="G2515" s="30"/>
+      <c r="H2515" s="30"/>
+    </row>
+    <row r="2516" spans="6:8">
+      <c r="F2516" s="30"/>
+      <c r="G2516" s="30"/>
+      <c r="H2516" s="30"/>
+    </row>
+    <row r="2517" spans="6:8">
+      <c r="F2517" s="30"/>
+      <c r="G2517" s="30"/>
+      <c r="H2517" s="30"/>
+    </row>
+    <row r="2518" spans="6:8">
+      <c r="F2518" s="30"/>
+      <c r="G2518" s="30"/>
+      <c r="H2518" s="30"/>
+    </row>
+    <row r="2519" spans="6:8">
+      <c r="F2519" s="30"/>
+      <c r="G2519" s="30"/>
+      <c r="H2519" s="30"/>
+    </row>
+    <row r="2520" spans="6:8">
+      <c r="F2520" s="30"/>
+      <c r="G2520" s="30"/>
+      <c r="H2520" s="30"/>
+    </row>
+    <row r="2521" spans="6:8">
+      <c r="F2521" s="30"/>
+      <c r="G2521" s="30"/>
+      <c r="H2521" s="30"/>
+    </row>
+    <row r="2522" spans="6:8">
+      <c r="F2522" s="30"/>
+      <c r="G2522" s="30"/>
+      <c r="H2522" s="30"/>
+    </row>
+    <row r="2523" spans="6:8">
+      <c r="F2523" s="30"/>
+      <c r="G2523" s="30"/>
+      <c r="H2523" s="30"/>
+    </row>
+    <row r="2524" spans="6:8">
+      <c r="F2524" s="30"/>
+      <c r="G2524" s="30"/>
+      <c r="H2524" s="30"/>
+    </row>
+    <row r="2525" spans="6:8">
+      <c r="F2525" s="30"/>
+      <c r="G2525" s="30"/>
+      <c r="H2525" s="30"/>
+    </row>
+    <row r="2534" spans="6:8">
+      <c r="F2534" s="30"/>
+      <c r="G2534" s="30"/>
+      <c r="H2534" s="30"/>
+    </row>
+    <row r="2551" spans="6:8">
+      <c r="F2551" s="30"/>
+      <c r="G2551" s="30"/>
+      <c r="H2551" s="30"/>
+    </row>
+    <row r="2568" spans="6:8">
+      <c r="F2568" s="30"/>
+      <c r="G2568" s="30"/>
+      <c r="H2568" s="30"/>
+    </row>
+    <row r="2585" spans="6:8">
+      <c r="F2585" s="30"/>
+      <c r="G2585" s="30"/>
+      <c r="H2585" s="30"/>
+    </row>
+    <row r="2602" spans="6:6">
+      <c r="F2602" s="30"/>
+    </row>
+    <row r="2619" spans="6:6">
+      <c r="F2619" s="30"/>
+    </row>
+    <row r="2636" spans="6:6">
+      <c r="F2636" s="30"/>
+    </row>
+    <row r="2653" spans="6:6">
+      <c r="F2653" s="30"/>
+    </row>
+    <row r="2670" spans="6:6">
+      <c r="F2670" s="30"/>
+    </row>
+    <row r="2687" spans="6:6">
+      <c r="F2687" s="30"/>
+    </row>
+    <row r="2704" spans="6:6">
+      <c r="F2704" s="30"/>
+    </row>
+    <row r="2721" spans="6:8">
+      <c r="F2721" s="30"/>
+      <c r="H2721" s="30"/>
+    </row>
+    <row r="2738" spans="6:6">
+      <c r="F2738" s="30"/>
+    </row>
+    <row r="2772" spans="6:6">
+      <c r="F2772" s="30"/>
+    </row>
+    <row r="2789" spans="6:6">
       <c r="F2789" s="30"/>
-      <c r="H2789" s="30"/>
-    </row>
-    <row r="2810" spans="6:6">
-      <c r="F2810" s="30"/>
-    </row>
-    <row r="2825" spans="6:8">
-      <c r="F2825" s="30"/>
-      <c r="G2825" s="30"/>
-      <c r="H2825" s="30"/>
-    </row>
-    <row r="2840" spans="6:8">
-      <c r="F2840" s="30"/>
-      <c r="H2840" s="30"/>
-    </row>
-    <row r="2855" spans="6:8">
-      <c r="F2855" s="30"/>
-      <c r="G2855" s="30"/>
-      <c r="H2855" s="30"/>
-    </row>
-    <row r="2871" spans="6:8">
-      <c r="F2871" s="30"/>
-      <c r="G2871" s="30"/>
-      <c r="H2871" s="30"/>
-    </row>
-    <row r="2879" spans="6:8">
-      <c r="F2879" s="30"/>
-      <c r="G2879" s="30"/>
-      <c r="H2879" s="30"/>
-    </row>
-    <row r="2907" spans="6:8">
-      <c r="F2907" s="30"/>
-      <c r="G2907" s="30"/>
-      <c r="H2907" s="30"/>
-    </row>
-    <row r="2915" spans="6:8">
-      <c r="F2915" s="30"/>
-      <c r="G2915" s="30"/>
-      <c r="H2915" s="30"/>
-    </row>
-    <row r="2922" spans="6:8">
-      <c r="F2922" s="30"/>
-      <c r="G2922" s="30"/>
-      <c r="H2922" s="30"/>
+    </row>
+    <row r="2812" spans="6:8">
+      <c r="F2812" s="30"/>
+      <c r="H2812" s="30"/>
+    </row>
+    <row r="2833" spans="6:8">
+      <c r="F2833" s="30"/>
+    </row>
+    <row r="2848" spans="6:8">
+      <c r="F2848" s="30"/>
+      <c r="G2848" s="30"/>
+      <c r="H2848" s="30"/>
+    </row>
+    <row r="2863" spans="6:8">
+      <c r="F2863" s="30"/>
+      <c r="H2863" s="30"/>
+    </row>
+    <row r="2878" spans="6:8">
+      <c r="F2878" s="30"/>
+      <c r="G2878" s="30"/>
+      <c r="H2878" s="30"/>
+    </row>
+    <row r="2894" spans="6:8">
+      <c r="F2894" s="30"/>
+      <c r="G2894" s="30"/>
+      <c r="H2894" s="30"/>
+    </row>
+    <row r="2902" spans="6:8">
+      <c r="F2902" s="30"/>
+      <c r="G2902" s="30"/>
+      <c r="H2902" s="30"/>
+    </row>
+    <row r="2930" spans="6:8">
+      <c r="F2930" s="30"/>
+      <c r="G2930" s="30"/>
+      <c r="H2930" s="30"/>
+    </row>
+    <row r="2938" spans="6:8">
+      <c r="F2938" s="30"/>
+      <c r="G2938" s="30"/>
+      <c r="H2938" s="30"/>
+    </row>
+    <row r="2945" spans="6:8">
+      <c r="F2945" s="30"/>
+      <c r="G2945" s="30"/>
+      <c r="H2945" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
